--- a/single-api/mainapi/swagger_modules.xlsx
+++ b/single-api/mainapi/swagger_modules.xlsx
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="F116" s="29" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G116" s="29" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H116" s="29" t="inlineStr">
         <is>
-          <t>3% (2/58)</t>
+          <t>84% (49/58)</t>
         </is>
       </c>
     </row>
@@ -42568,7 +42568,7 @@
       </c>
       <c r="F1296" s="44" t="inlineStr">
         <is>
-          <t>添加广告组到标签（含后置清理,可重复） — 100%</t>
+          <t>将广告组加入AdGroup标签 — 100%</t>
         </is>
       </c>
     </row>
@@ -42596,11 +42596,11 @@
       </c>
       <c r="F1297" s="44" t="inlineStr">
         <is>
-          <t>添加ASIN到标签（含后置清理,可重复） — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1298">
+          <t>将ASIN加入ASIN标签（含后置移除，可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298" ht="16" customHeight="1">
       <c r="A1298" s="41" t="n"/>
       <c r="B1298" s="27" t="inlineStr">
         <is>
@@ -42622,8 +42622,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1299">
+      <c r="F1298" s="44" t="inlineStr">
+        <is>
+          <t>为Campaign标签新增匹配规则 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299" ht="16" customHeight="1">
       <c r="A1299" s="41" t="n"/>
       <c r="B1299" s="23" t="inlineStr">
         <is>
@@ -42645,8 +42650,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1300">
+      <c r="F1299" s="44" t="inlineStr">
+        <is>
+          <t>应用匹配规则差异(加入后还原,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300" ht="16" customHeight="1">
       <c r="A1300" s="41" t="n"/>
       <c r="B1300" s="27" t="inlineStr">
         <is>
@@ -42668,8 +42678,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1301">
+      <c r="F1300" s="44" t="inlineStr">
+        <is>
+          <t>批量创建关键词标签 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301" ht="16" customHeight="1">
       <c r="A1301" s="41" t="n"/>
       <c r="B1301" s="23" t="inlineStr">
         <is>
@@ -42689,6 +42704,11 @@
       <c r="E1301" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1301" s="44" t="inlineStr">
+        <is>
+          <t>批量设置Campaign标签ACOS/ROAS目标 — 100%</t>
         </is>
       </c>
     </row>
@@ -42714,8 +42734,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1303">
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>已作为CreateTagName/UpdateMatchRule等case的后置清理步骤覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303" ht="16" customHeight="1">
       <c r="A1303" s="41" t="n"/>
       <c r="B1303" s="23" t="inlineStr">
         <is>
@@ -42735,6 +42760,11 @@
       <c r="E1303" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1303" s="44" t="inlineStr">
+        <is>
+          <t>批量从标签删除Campaign(含前置加入,可重复) — 100%</t>
         </is>
       </c>
     </row>
@@ -42760,8 +42790,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1305">
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>已作为CreateKeywordTagging case的后置清理步骤覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305" ht="16" customHeight="1">
       <c r="A1305" s="41" t="n"/>
       <c r="B1305" s="23" t="inlineStr">
         <is>
@@ -42783,8 +42818,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1306">
+      <c r="F1305" s="44" t="inlineStr">
+        <is>
+          <t>公式版设置Campaign标签目标 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306" ht="16" customHeight="1">
       <c r="A1306" s="41" t="n"/>
       <c r="B1306" s="27" t="inlineStr">
         <is>
@@ -42804,6 +42844,11 @@
       <c r="E1306" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1306" s="44" t="inlineStr">
+        <is>
+          <t>修改ASIN标签所有者(含后置还原,可重复) — 100%</t>
         </is>
       </c>
     </row>
@@ -42829,6 +42874,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>30天0调用，功能极少使用，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1308" ht="16" customHeight="1">
       <c r="A1308" s="41" t="n"/>
@@ -42880,6 +42930,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>30天0调用，已被CheckCampaignToTagV2替代，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1310" ht="32" customHeight="1">
       <c r="A1310" s="41" t="n"/>
@@ -42905,12 +42960,11 @@
       </c>
       <c r="F1310" s="44" t="inlineStr">
         <is>
-          <t>type=0 指定标签批量检查 — 60%
-type=1 大批量Campaign检查 — 40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1311">
+          <t>检查Campaign是否可被加入标签 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311" ht="16" customHeight="1">
       <c r="A1311" s="41" t="n"/>
       <c r="B1311" s="23" t="inlineStr">
         <is>
@@ -42932,8 +42986,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1312">
+      <c r="F1311" s="44" t="inlineStr">
+        <is>
+          <t>创建AdGroup子标签(自清理父标签,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312" ht="16" customHeight="1">
       <c r="A1312" s="41" t="n"/>
       <c r="B1312" s="27" t="inlineStr">
         <is>
@@ -42955,8 +43014,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1313">
+      <c r="F1312" s="44" t="inlineStr">
+        <is>
+          <t>创建AdGroup标签(含后置清理,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313" ht="16" customHeight="1">
       <c r="A1313" s="41" t="n"/>
       <c r="B1313" s="23" t="inlineStr">
         <is>
@@ -42976,6 +43040,11 @@
       <c r="E1313" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1313" s="44" t="inlineStr">
+        <is>
+          <t>创建标签备注(含后置清理,可重复) — 100%</t>
         </is>
       </c>
     </row>
@@ -43008,7 +43077,7 @@
         </is>
       </c>
     </row>
-    <row r="1315">
+    <row r="1315" ht="16" customHeight="1">
       <c r="A1315" s="41" t="n"/>
       <c r="B1315" s="23" t="inlineStr">
         <is>
@@ -43030,8 +43099,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1316">
+      <c r="F1315" s="44" t="inlineStr">
+        <is>
+          <t>创建Campaign子标签(自清理临时父标签,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316" ht="16" customHeight="1">
       <c r="A1316" s="41" t="n"/>
       <c r="B1316" s="27" t="inlineStr">
         <is>
@@ -43051,6 +43125,11 @@
       <c r="E1316" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1316" s="44" t="inlineStr">
+        <is>
+          <t>创建关键词标签（含后置清理，可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -43078,11 +43157,11 @@
       </c>
       <c r="F1317" s="44" t="inlineStr">
         <is>
-          <t>创建顶级Campaign标签（含后置清理,可重复） — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1318">
+          <t>创建Campaign标签（含后置清理，可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318" ht="16" customHeight="1">
       <c r="A1318" s="41" t="n"/>
       <c r="B1318" s="27" t="inlineStr">
         <is>
@@ -43102,6 +43181,11 @@
       <c r="E1318" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1318" s="44" t="inlineStr">
+        <is>
+          <t>从AdGroup标签移除广告组(含前置,可重复) — 100%</t>
         </is>
       </c>
     </row>
@@ -43127,8 +43211,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1320">
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>已作为AdGroup标签系列case的后置清理步骤覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320" ht="16" customHeight="1">
       <c r="A1320" s="41" t="n"/>
       <c r="B1320" s="27" t="inlineStr">
         <is>
@@ -43150,8 +43239,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1321">
+      <c r="F1320" s="44" t="inlineStr">
+        <is>
+          <t>删除标签备注(含前置,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321" ht="16" customHeight="1">
       <c r="A1321" s="41" t="n"/>
       <c r="B1321" s="23" t="inlineStr">
         <is>
@@ -43171,6 +43265,11 @@
       <c r="E1321" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1321" s="44" t="inlineStr">
+        <is>
+          <t>删除ASIN标签(专属fixture,幂等可重复) — 100%</t>
         </is>
       </c>
     </row>
@@ -43224,6 +43323,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>30天0调用，疑似废弃接口，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1324">
       <c r="A1324" s="41" t="n"/>
@@ -43247,6 +43351,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>30天0调用，删除关键词标签实际走BulkDeleteKeywordTag，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1325" ht="16" customHeight="1">
       <c r="A1325" s="41" t="n"/>
@@ -43272,11 +43381,11 @@
       </c>
       <c r="F1325" s="44" t="inlineStr">
         <is>
-          <t>重命名ASIN标签（含后置还原,可重复） — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1326">
+          <t>修改ASIN子标签名称（含后置还原，可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326" ht="16" customHeight="1">
       <c r="A1326" s="41" t="n"/>
       <c r="B1326" s="27" t="inlineStr">
         <is>
@@ -43296,6 +43405,11 @@
       <c r="E1326" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1326" s="44" t="inlineStr">
+        <is>
+          <t>根据AdGroup标签获取广告组列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -43323,8 +43437,7 @@
       </c>
       <c r="F1327" s="44" t="inlineStr">
         <is>
-          <t>无参数（默认） — 95.7%
-isCheckEdit=true — 4.3%</t>
+          <t>获取所有AdGroup标签列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -43350,6 +43463,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>30天0调用，已被GetAdGroupTagByAdgroupForPermission替代，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1329" ht="16" customHeight="1">
       <c r="A1329" s="41" t="n"/>
@@ -43431,8 +43549,7 @@
       </c>
       <c r="F1331" s="44" t="inlineStr">
         <is>
-          <t>无参数（默认） — 96.6%
-isCheckEdit=true — 3.4%</t>
+          <t>获取全部ASIN标签列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -43460,7 +43577,7 @@
       </c>
       <c r="F1332" s="44" t="inlineStr">
         <is>
-          <t>isCheckEdit=true — 99.9%</t>
+          <t>获取全部关键词标签列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -43488,7 +43605,7 @@
       </c>
       <c r="F1333" s="44" t="inlineStr">
         <is>
-          <t>查询Campaign标签备注 — 100%</t>
+          <t>查询标签备注信息 — 100%</t>
         </is>
       </c>
     </row>
@@ -43516,7 +43633,7 @@
       </c>
       <c r="F1334" s="44" t="inlineStr">
         <is>
-          <t>按标签查ASIN列表 — 100%</t>
+          <t>根据ASIN标签获取ASIN列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -43542,6 +43659,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>30天0调用，已被GetMutilCampaignByCampaignTag替代，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1336">
       <c r="A1336" s="41" t="n"/>
@@ -43565,6 +43687,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>30天0调用，标签转移功能低频，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1337" ht="16" customHeight="1">
       <c r="A1337" s="41" t="n"/>
@@ -43590,7 +43717,7 @@
       </c>
       <c r="F1337" s="44" t="inlineStr">
         <is>
-          <t>按profileIds查Campaign标签 — 100%</t>
+          <t>获取Campaign标签（按Profile过滤） — 30%</t>
         </is>
       </c>
     </row>
@@ -43616,6 +43743,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>30天0调用，疑似GetCampaignTag旧版POST变体，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1339">
       <c r="A1339" s="41" t="n"/>
@@ -43639,8 +43771,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1340" ht="16" customHeight="1">
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>30天0调用，标签转移功能低频，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340" ht="32" customHeight="1">
       <c r="A1340" s="41" t="n"/>
       <c r="B1340" s="27" t="inlineStr">
         <is>
@@ -43664,7 +43801,8 @@
       </c>
       <c r="F1340" s="44" t="inlineStr">
         <is>
-          <t>按标签查关键词 — 100%</t>
+          <t>根据标签获取关键词列表 — 100%
+按标签查关键词 — 100%</t>
         </is>
       </c>
     </row>
@@ -43720,7 +43858,7 @@
       </c>
       <c r="F1342" s="44" t="inlineStr">
         <is>
-          <t>按标签查多profile Campaign — 100%</t>
+          <t>批量查询Campaign标签下的Campaign — 100%</t>
         </is>
       </c>
     </row>
@@ -43748,7 +43886,7 @@
       </c>
       <c r="F1343" s="44" t="inlineStr">
         <is>
-          <t>查询多标签匹配规则差异 — 100%</t>
+          <t>查询Campaign标签匹配规则差异 — 100%</t>
         </is>
       </c>
     </row>
@@ -43774,6 +43912,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>已作为AddAsinsToAsinTagging/SaveAsinToTag case的后置清理步骤覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1345" ht="16" customHeight="1">
       <c r="A1345" s="41" t="n"/>
@@ -43825,8 +43968,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1347">
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>已作为GetKeywordsByTag case的前置造数步骤覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347" ht="16" customHeight="1">
       <c r="A1347" s="41" t="n"/>
       <c r="B1347" s="23" t="inlineStr">
         <is>
@@ -43848,8 +43996,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1348">
+      <c r="F1347" s="44" t="inlineStr">
+        <is>
+          <t>修改AdGroup标签名称(自清理,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348" ht="16" customHeight="1">
       <c r="A1348" s="41" t="n"/>
       <c r="B1348" s="27" t="inlineStr">
         <is>
@@ -43869,6 +44022,11 @@
       <c r="E1348" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1348" s="44" t="inlineStr">
+        <is>
+          <t>修改标签备注(自清理,可重复) — 100%</t>
         </is>
       </c>
     </row>
@@ -43894,6 +44052,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>已作为DeleteCampaignsFromTag/BulkDeleteCampaignsFromTag case的前置步骤覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1350" ht="16" customHeight="1">
       <c r="A1350" s="41" t="n"/>
@@ -43919,11 +44082,11 @@
       </c>
       <c r="F1350" s="44" t="inlineStr">
         <is>
-          <t>重命名Campaign标签（含后置还原,可重复） — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1351">
+          <t>修改Campaign标签名称（含后置还原，可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351" ht="16" customHeight="1">
       <c r="A1351" s="41" t="n"/>
       <c r="B1351" s="23" t="inlineStr">
         <is>
@@ -43945,8 +44108,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1352">
+      <c r="F1351" s="44" t="inlineStr">
+        <is>
+          <t>修改关键词标签名称和描述（含后置还原，可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352" ht="16" customHeight="1">
       <c r="A1352" s="41" t="n"/>
       <c r="B1352" s="27" t="inlineStr">
         <is>
@@ -43968,8 +44136,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1353">
+      <c r="F1352" s="44" t="inlineStr">
+        <is>
+          <t>修改Campaign标签匹配规则(自清理临时标签,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353" ht="16" customHeight="1">
       <c r="A1353" s="41" t="n"/>
       <c r="B1353" s="23" t="inlineStr">
         <is>
@@ -43989,6 +44162,11 @@
       <c r="E1353" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1353" s="44" t="inlineStr">
+        <is>
+          <t>修改Campaign标签所有者（含后置还原，可重复） — 100%</t>
         </is>
       </c>
     </row>

--- a/single-api/mainapi/swagger_modules.xlsx
+++ b/single-api/mainapi/swagger_modules.xlsx
@@ -2455,6 +2455,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F49" s="29" t="n">
+        <v>39</v>
+      </c>
+      <c r="G49" s="29" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="inlineStr">
+        <is>
+          <t>100% (28/28)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="41" t="n"/>
@@ -3054,6 +3067,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F67" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H67" s="29" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="41" t="n"/>
@@ -3130,6 +3156,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F70" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>100% (6/6)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="41" t="n"/>
@@ -3219,6 +3258,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F73" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G73" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H73" s="29" t="inlineStr">
+        <is>
+          <t>100% (18/18)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="41" t="n"/>
@@ -3410,6 +3462,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F79" s="29" t="n">
+        <v>50</v>
+      </c>
+      <c r="G79" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H79" s="29" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="41" t="n"/>
@@ -3499,6 +3564,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F82" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="G82" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H82" s="29" t="inlineStr">
+        <is>
+          <t>100% (13/13)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="41" t="n"/>
@@ -3588,6 +3666,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F85" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G85" s="29" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="H85" s="29" t="inlineStr">
+        <is>
+          <t>100% (7/7)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="41" t="n"/>
@@ -3664,6 +3755,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F88" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G88" s="29" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="H88" s="29" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="41" t="n"/>
@@ -3753,6 +3857,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F91" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H91" s="29" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="41" t="n"/>
@@ -3829,6 +3946,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F94" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G94" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H94" s="29" t="inlineStr">
+        <is>
+          <t>100% (6/6)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="41" t="n"/>
@@ -3918,6 +4048,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F97" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="G97" s="29" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="H97" s="29" t="inlineStr">
+        <is>
+          <t>100% (18/18)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="41" t="n"/>
@@ -4007,6 +4150,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F100" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H100" s="29" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="41" t="n"/>
@@ -4096,6 +4252,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F103" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="G103" s="29" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H103" s="29" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="41" t="n"/>
@@ -4185,6 +4354,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F106" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="G106" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H106" s="29" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="41" t="n"/>
@@ -4274,6 +4456,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F109" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="G109" s="29" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="H109" s="29" t="inlineStr">
+        <is>
+          <t>100% (14/14)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="41" t="n"/>
@@ -4350,6 +4545,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F112" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="G112" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H112" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="41" t="n"/>
@@ -4439,6 +4647,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F115" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G115" s="29" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H115" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="41" t="n"/>
@@ -4528,6 +4749,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F118" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H118" s="29" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="41" t="n"/>
@@ -4615,6 +4849,19 @@
       <c r="E121" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F121" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G121" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H121" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
         </is>
       </c>
     </row>
@@ -23668,13 +23915,14 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F575" s="36" t="inlineStr">
-        <is>
-          <t>归档SP Campaign(create新建后归档,自包含可重复) — 50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
+      <c r="F575" s="44" t="inlineStr">
+        <is>
+          <t>创建SP手动广告系列+广告组(含后置归档,可重复) — 60.7%
+创建SP自动广告系列+广告组(含后置归档,可重复) — 39.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="16" customHeight="1">
       <c r="A576" s="41" t="n"/>
       <c r="B576" s="27" t="inlineStr">
         <is>
@@ -23696,8 +23944,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="577">
+      <c r="F576" s="44" t="inlineStr">
+        <is>
+          <t>在已有Campaign下新建广告组(含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="48" customHeight="1">
       <c r="A577" s="41" t="n"/>
       <c r="B577" s="23" t="inlineStr">
         <is>
@@ -23719,8 +23972,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="578">
+      <c r="F577" s="44" t="inlineStr">
+        <is>
+          <t>批量创建exact匹配关键词(含后置归档,可重复) — 39.2%
+批量创建phrase匹配关键词(含后置归档,可重复) — 22.2%
+批量创建broad匹配关键词(含后置归档,可重复) — 11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="16" customHeight="1">
       <c r="A578" s="41" t="n"/>
       <c r="B578" s="27" t="inlineStr">
         <is>
@@ -23742,8 +24002,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="579">
+      <c r="F578" s="44" t="inlineStr">
+        <is>
+          <t>跨广告组批量创建关键词(含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="16" customHeight="1">
       <c r="A579" s="41" t="n"/>
       <c r="B579" s="23" t="inlineStr">
         <is>
@@ -23765,8 +24030,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="580">
+      <c r="F579" s="44" t="inlineStr">
+        <is>
+          <t>跨Profile批量创建ASIN定向(含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="48" customHeight="1">
       <c r="A580" s="41" t="n"/>
       <c r="B580" s="27" t="inlineStr">
         <is>
@@ -23788,8 +24058,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="581">
+      <c r="F580" s="44" t="inlineStr">
+        <is>
+          <t>创建asinSameAs定向(含后置归档,可重复) — 79.8%
+创建asinCategorySameAs定向(含后置归档,可重复) — 12.8%
+创建asinExpandedFrom定向(含后置归档,可重复) — 7.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="16" customHeight="1">
       <c r="A581" s="41" t="n"/>
       <c r="B581" s="23" t="inlineStr">
         <is>
@@ -23811,8 +24088,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="582">
+      <c r="F581" s="44" t="inlineStr">
+        <is>
+          <t>创建SD广告系列(含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="16" customHeight="1">
       <c r="A582" s="41" t="n"/>
       <c r="B582" s="27" t="inlineStr">
         <is>
@@ -23834,8 +24116,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="583">
+      <c r="F582" s="44" t="inlineStr">
+        <is>
+          <t>在已有SD Campaign下创建广告组(含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="16" customHeight="1">
       <c r="A583" s="41" t="n"/>
       <c r="B583" s="23" t="inlineStr">
         <is>
@@ -23857,8 +24144,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="584">
+      <c r="F583" s="44" t="inlineStr">
+        <is>
+          <t>单ASIN查询SOV信息 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="16" customHeight="1">
       <c r="A584" s="41" t="n"/>
       <c r="B584" s="27" t="inlineStr">
         <is>
@@ -23880,8 +24172,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="585">
+      <c r="F584" s="44" t="inlineStr">
+        <is>
+          <t>查询ASIN广告资质状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="16" customHeight="1">
       <c r="A585" s="41" t="n"/>
       <c r="B585" s="23" t="inlineStr">
         <is>
@@ -23903,8 +24200,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="586">
+      <c r="F585" s="44" t="inlineStr">
+        <is>
+          <t>ASIN标签维度效果数据分页查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="16" customHeight="1">
       <c r="A586" s="41" t="n"/>
       <c r="B586" s="27" t="inlineStr">
         <is>
@@ -23926,8 +24228,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="587">
+      <c r="F586" s="44" t="inlineStr">
+        <is>
+          <t>按assetId批量查询素材 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="16" customHeight="1">
       <c r="A587" s="41" t="n"/>
       <c r="B587" s="23" t="inlineStr">
         <is>
@@ -23949,8 +24256,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="588">
+      <c r="F587" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN查询广告下商品广告</t>
+        </is>
+      </c>
+    </row>
+    <row r="588" ht="16" customHeight="1">
       <c r="A588" s="41" t="n"/>
       <c r="B588" s="27" t="inlineStr">
         <is>
@@ -23972,8 +24284,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="589">
+      <c r="F588" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN列表获取SD受众推荐 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" ht="16" customHeight="1">
       <c r="A589" s="41" t="n"/>
       <c r="B589" s="23" t="inlineStr">
         <is>
@@ -23995,8 +24312,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="590">
+      <c r="F589" s="44" t="inlineStr">
+        <is>
+          <t>T00030相似商品定向出价推荐 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="590" ht="16" customHeight="1">
       <c r="A590" s="41" t="n"/>
       <c r="B590" s="27" t="inlineStr">
         <is>
@@ -24018,8 +24340,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="591">
+      <c r="F590" s="44" t="inlineStr">
+        <is>
+          <t>查询SD创意审核状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="32" customHeight="1">
       <c r="A591" s="41" t="n"/>
       <c r="B591" s="23" t="inlineStr">
         <is>
@@ -24041,8 +24368,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="592">
+      <c r="F591" s="44" t="inlineStr">
+        <is>
+          <t>IMAGE创意预览 — 90%
+VIDEO创意预览 — 9.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="16" customHeight="1">
       <c r="A592" s="41" t="n"/>
       <c r="B592" s="27" t="inlineStr">
         <is>
@@ -24064,8 +24397,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="593">
+      <c r="F592" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN获取SD创意标题推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="16" customHeight="1">
       <c r="A593" s="41" t="n"/>
       <c r="B593" s="23" t="inlineStr">
         <is>
@@ -24087,8 +24425,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="594">
+      <c r="F593" s="44" t="inlineStr">
+        <is>
+          <t>T00030商品类目推荐 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="16" customHeight="1">
       <c r="A594" s="41" t="n"/>
       <c r="B594" s="27" t="inlineStr">
         <is>
@@ -24110,8 +24453,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="595">
+      <c r="F594" s="44" t="inlineStr">
+        <is>
+          <t>T00030商品定向推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="64" customHeight="1">
       <c r="A595" s="41" t="n"/>
       <c r="B595" s="23" t="inlineStr">
         <is>
@@ -24133,8 +24481,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="596">
+      <c r="F595" s="44" t="inlineStr">
+        <is>
+          <t>按LOGO类型搜索素材 — 59.4%
+按BACKGROUND VIDEO类型搜索素材 — 25.2%
+多类型组合搜索素材(图文混合) — 11.2%
+不限类型浏览全部素材 — 3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="16" customHeight="1">
       <c r="A596" s="41" t="n"/>
       <c r="B596" s="27" t="inlineStr">
         <is>
@@ -24156,8 +24512,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="597">
+      <c r="F596" s="44" t="inlineStr">
+        <is>
+          <t>关键词批量建议出价 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="48" customHeight="1">
       <c r="A597" s="41" t="n"/>
       <c r="B597" s="23" t="inlineStr">
         <is>
@@ -24179,8 +24540,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="598">
+      <c r="F597" s="44" t="inlineStr">
+        <is>
+          <t>新建广告组ASIN定向建议出价(legacyForSales) — 48.6%
+新建广告组ASIN定向建议出价(autoForSales) — 42.6%
+新建广告组ASIN定向建议出价(manual) — 8.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="16" customHeight="1">
       <c r="A598" s="41" t="n"/>
       <c r="B598" s="27" t="inlineStr">
         <is>
@@ -24202,8 +24570,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="599">
+      <c r="F598" s="44" t="inlineStr">
+        <is>
+          <t>关键词/PAT批量建议出价(V4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="599" ht="16" customHeight="1">
       <c r="A599" s="41" t="n"/>
       <c r="B599" s="23" t="inlineStr">
         <is>
@@ -24225,8 +24598,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="600">
+      <c r="F599" s="44" t="inlineStr">
+        <is>
+          <t>通过URL上传AI生成素材</t>
+        </is>
+      </c>
+    </row>
+    <row r="600" ht="16" customHeight="1">
       <c r="A600" s="41" t="n"/>
       <c r="B600" s="27" t="inlineStr">
         <is>
@@ -24248,8 +24626,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="601">
+      <c r="F600" s="44" t="inlineStr">
+        <is>
+          <t>上传素材文件(multipart) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="16" customHeight="1">
       <c r="A601" s="41" t="n"/>
       <c r="B601" s="23" t="inlineStr">
         <is>
@@ -24271,8 +24654,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="602">
+      <c r="F601" s="44" t="inlineStr">
+        <is>
+          <t>通过URL上传素材(含后置说明,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="602" ht="16" customHeight="1">
       <c r="A602" s="41" t="n"/>
       <c r="B602" s="27" t="inlineStr">
         <is>
@@ -24294,9 +24682,9 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F602" t="inlineStr">
-        <is>
-          <t>归档SP Campaign(create新建后归档,自包含可重复) — 50%</t>
+      <c r="F602" s="44" t="inlineStr">
+        <is>
+          <t>上传SD创意图片(multipart)</t>
         </is>
       </c>
     </row>
@@ -27111,7 +27499,7 @@
         </is>
       </c>
     </row>
-    <row r="705">
+    <row r="705" ht="16" customHeight="1">
       <c r="A705" s="41" t="n"/>
       <c r="B705" s="23" t="inlineStr">
         <is>
@@ -27131,6 +27519,11 @@
       <c r="E705" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F705" s="44" t="inlineStr">
+        <is>
+          <t>按assetId批量查询素材 — 100%</t>
         </is>
       </c>
     </row>
@@ -31381,7 +31774,7 @@
         </is>
       </c>
     </row>
-    <row r="870">
+    <row r="870" ht="16" customHeight="1">
       <c r="A870" s="41" t="n"/>
       <c r="B870" s="26" t="inlineStr">
         <is>
@@ -31403,8 +31796,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="871">
+      <c r="F870" s="44" t="inlineStr">
+        <is>
+          <t>按ProfileId+AdGroupId获取PAT推荐 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="871" ht="16" customHeight="1">
       <c r="A871" s="41" t="n"/>
       <c r="B871" s="23" t="inlineStr">
         <is>
@@ -31426,8 +31824,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="872">
+      <c r="F871" s="44" t="inlineStr">
+        <is>
+          <t>按国家+ASIN批量获取商品信息 — 96.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="872" ht="16" customHeight="1">
       <c r="A872" s="41" t="n"/>
       <c r="B872" s="27" t="inlineStr">
         <is>
@@ -31449,8 +31852,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="873">
+      <c r="F872" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN+ProfileId查询单商品信息 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="873" ht="16" customHeight="1">
       <c r="A873" s="41" t="n"/>
       <c r="B873" s="23" t="inlineStr">
         <is>
@@ -31470,6 +31878,11 @@
       <c r="E873" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F873" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN+多ProfileId查询商品透视信息 — 100%</t>
         </is>
       </c>
     </row>
@@ -31524,7 +31937,7 @@
         </is>
       </c>
     </row>
-    <row r="876">
+    <row r="876" ht="16" customHeight="1">
       <c r="A876" s="41" t="n"/>
       <c r="B876" s="26" t="inlineStr">
         <is>
@@ -31546,8 +31959,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="877">
+      <c r="F876" s="44" t="inlineStr">
+        <is>
+          <t>按国家查询亚马逊类目树</t>
+        </is>
+      </c>
+    </row>
+    <row r="877" ht="16" customHeight="1">
       <c r="A877" s="41" t="n"/>
       <c r="B877" s="23" t="inlineStr">
         <is>
@@ -31569,8 +31987,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="878">
+      <c r="F877" s="44" t="inlineStr">
+        <is>
+          <t>按profileId查询假日类目分组 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="878" ht="16" customHeight="1">
       <c r="A878" s="41" t="n"/>
       <c r="B878" s="27" t="inlineStr">
         <is>
@@ -31592,8 +32015,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="879">
+      <c r="F878" s="44" t="inlineStr">
+        <is>
+          <t>按类目+年份分页查询假日关键词热度数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="879" ht="16" customHeight="1">
       <c r="A879" s="41" t="n"/>
       <c r="B879" s="23" t="inlineStr">
         <is>
@@ -31615,8 +32043,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="880">
+      <c r="F879" s="44" t="inlineStr">
+        <is>
+          <t>按搜索词+起始日期查询上周ASIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="880" ht="16" customHeight="1">
       <c r="A880" s="41" t="n"/>
       <c r="B880" s="27" t="inlineStr">
         <is>
@@ -31638,8 +32071,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="881">
+      <c r="F880" s="44" t="inlineStr">
+        <is>
+          <t>按搜索词查询最新ASIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="881" ht="16" customHeight="1">
       <c r="A881" s="41" t="n"/>
       <c r="B881" s="23" t="inlineStr">
         <is>
@@ -31659,6 +32097,11 @@
       <c r="E881" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F881" s="44" t="inlineStr">
+        <is>
+          <t>按搜索词批量查询最新搜索排名</t>
         </is>
       </c>
     </row>
@@ -32301,7 +32744,7 @@
         </is>
       </c>
     </row>
-    <row r="904">
+    <row r="904" ht="16" customHeight="1">
       <c r="A904" s="41" t="n"/>
       <c r="B904" s="26" t="inlineStr">
         <is>
@@ -32323,8 +32766,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="905">
+      <c r="F904" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="905" ht="16" customHeight="1">
       <c r="A905" s="41" t="n"/>
       <c r="B905" s="23" t="inlineStr">
         <is>
@@ -32346,8 +32794,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="906">
+      <c r="F905" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="906" ht="16" customHeight="1">
       <c r="A906" s="41" t="n"/>
       <c r="B906" s="27" t="inlineStr">
         <is>
@@ -32369,8 +32822,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="907">
+      <c r="F906" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="907" ht="16" customHeight="1">
       <c r="A907" s="41" t="n"/>
       <c r="B907" s="23" t="inlineStr">
         <is>
@@ -32392,8 +32850,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="908">
+      <c r="F907" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="908" ht="16" customHeight="1">
       <c r="A908" s="41" t="n"/>
       <c r="B908" s="27" t="inlineStr">
         <is>
@@ -32415,8 +32878,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="909">
+      <c r="F908" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="909" ht="16" customHeight="1">
       <c r="A909" s="41" t="n"/>
       <c r="B909" s="23" t="inlineStr">
         <is>
@@ -32438,8 +32906,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="910">
+      <c r="F909" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="910" ht="16" customHeight="1">
       <c r="A910" s="41" t="n"/>
       <c r="B910" s="27" t="inlineStr">
         <is>
@@ -32461,8 +32934,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="911">
+      <c r="F910" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="911" ht="16" customHeight="1">
       <c r="A911" s="41" t="n"/>
       <c r="B911" s="23" t="inlineStr">
         <is>
@@ -32484,8 +32962,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="912">
+      <c r="F911" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="912" ht="16" customHeight="1">
       <c r="A912" s="41" t="n"/>
       <c r="B912" s="27" t="inlineStr">
         <is>
@@ -32507,8 +32990,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="913">
+      <c r="F912" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="913" ht="16" customHeight="1">
       <c r="A913" s="41" t="n"/>
       <c r="B913" s="23" t="inlineStr">
         <is>
@@ -32530,8 +33018,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="914">
+      <c r="F913" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="914" ht="16" customHeight="1">
       <c r="A914" s="41" t="n"/>
       <c r="B914" s="27" t="inlineStr">
         <is>
@@ -32553,8 +33046,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="915">
+      <c r="F914" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="915" ht="16" customHeight="1">
       <c r="A915" s="41" t="n"/>
       <c r="B915" s="23" t="inlineStr">
         <is>
@@ -32576,8 +33074,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="916">
+      <c r="F915" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="916" ht="16" customHeight="1">
       <c r="A916" s="41" t="n"/>
       <c r="B916" s="27" t="inlineStr">
         <is>
@@ -32599,8 +33102,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="917">
+      <c r="F916" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="917" ht="16" customHeight="1">
       <c r="A917" s="41" t="n"/>
       <c r="B917" s="23" t="inlineStr">
         <is>
@@ -32622,8 +33130,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="918">
+      <c r="F917" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="918" ht="16" customHeight="1">
       <c r="A918" s="41" t="n"/>
       <c r="B918" s="27" t="inlineStr">
         <is>
@@ -32645,8 +33158,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="919">
+      <c r="F918" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="919" ht="16" customHeight="1">
       <c r="A919" s="41" t="n"/>
       <c r="B919" s="23" t="inlineStr">
         <is>
@@ -32668,8 +33186,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="920">
+      <c r="F919" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="920" ht="16" customHeight="1">
       <c r="A920" s="41" t="n"/>
       <c r="B920" s="27" t="inlineStr">
         <is>
@@ -32691,8 +33214,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="921">
+      <c r="F920" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="921" ht="16" customHeight="1">
       <c r="A921" s="41" t="n"/>
       <c r="B921" s="23" t="inlineStr">
         <is>
@@ -32712,6 +33240,11 @@
       <c r="E921" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F921" s="44" t="inlineStr">
+        <is>
+          <t>Happy Path</t>
         </is>
       </c>
     </row>
@@ -34896,7 +35429,7 @@
         </is>
       </c>
     </row>
-    <row r="1000">
+    <row r="1000" ht="112" customHeight="1">
       <c r="A1000" s="41" t="n"/>
       <c r="B1000" s="26" t="inlineStr">
         <is>
@@ -34918,8 +35451,19 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1001">
+      <c r="F1000" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=1+无标签过滤+无广告类型过滤 — 77.8%
+TimeType=1+无标签过滤+含CampaignTypes过滤(sponsoredDisplay) — 10.0%
+TimeType=1+含CampaignTags过滤+无广告类型过滤 — 4.0%
+TimeType=2+无标签过滤+无广告类型过滤 — 1.4%
+TimeType=1+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts) — 1.4%
+TimeType=3+无标签过滤+无广告类型过滤 — 1.2%
+TimeType=3+含CampaignTags过滤+无广告类型过滤 — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001" ht="96" customHeight="1">
       <c r="A1001" s="41" t="n"/>
       <c r="B1001" s="23" t="inlineStr">
         <is>
@@ -34941,8 +35485,18 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1002">
+      <c r="F1001" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=1+无标签过滤+无广告类型过滤 — 77.8%
+TimeType=1+无标签过滤+含CampaignTypes过滤(sponsoredProducts) — 9.4%
+TimeType=1+含CampaignTags过滤+无广告类型过滤 — 3.6%
+TimeType=1+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 1.8%
+TimeType=3+无标签过滤+无广告类型过滤 — 1.8%
+TimeType=0+无标签过滤+无广告类型过滤 — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002" ht="64" customHeight="1">
       <c r="A1002" s="41" t="n"/>
       <c r="B1002" s="27" t="inlineStr">
         <is>
@@ -34964,8 +35518,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1003">
+      <c r="F1002" s="44" t="inlineStr">
+        <is>
+          <t>无TimeType+无标签过滤+无广告类型过滤 — 84.2%
+无TimeType+无标签过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 9.2%
+无TimeType+含CampaignTags过滤+无广告类型过滤 — 3.6%
+无TimeType+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003" ht="112" customHeight="1">
       <c r="A1003" s="41" t="n"/>
       <c r="B1003" s="23" t="inlineStr">
         <is>
@@ -34987,8 +35549,19 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1004">
+      <c r="F1003" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0+无标签过滤+无广告类型过滤 — 73.4%
+TimeType=0+无标签过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 7.6%
+TimeType=3+无标签过滤+无广告类型过滤 — 7.0%
+TimeType=0+含CampaignTags过滤+无广告类型过滤 — 5.2%
+TimeType=0+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 2.6%
+TimeType=3+无标签过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 2.4%
+TimeType=3+含CampaignTags过滤+无广告类型过滤 — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004" ht="96" customHeight="1">
       <c r="A1004" s="41" t="n"/>
       <c r="B1004" s="27" t="inlineStr">
         <is>
@@ -35010,8 +35583,18 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1005">
+      <c r="F1004" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=1+无标签过滤+无广告类型过滤 — 78.6%
+TimeType=1+无标签过滤+含CampaignTypes过滤(sponsoredProducts) — 8.4%
+TimeType=1+含CampaignTags过滤+无广告类型过滤 — 3.4%
+TimeType=3+无标签过滤+无广告类型过滤 — 2.2%
+TimeType=1+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 1.4%
+TimeType=3+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005" ht="96" customHeight="1">
       <c r="A1005" s="41" t="n"/>
       <c r="B1005" s="23" t="inlineStr">
         <is>
@@ -35033,8 +35616,18 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1006">
+      <c r="F1005" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=1+无标签过滤+无广告类型过滤 — 79.2%
+TimeType=1+无标签过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 7.4%
+TimeType=1+含CampaignTags过滤+无广告类型过滤 — 3.8%
+TimeType=3+无标签过滤+无广告类型过滤 — 2.2%
+TimeType=0+无标签过滤+无广告类型过滤 — 2.0%
+TimeType=1+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 1.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006" ht="96" customHeight="1">
       <c r="A1006" s="41" t="n"/>
       <c r="B1006" s="27" t="inlineStr">
         <is>
@@ -35056,8 +35649,18 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1007">
+      <c r="F1006" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=1+无标签过滤+无广告类型过滤 — 78.8%
+TimeType=1+无标签过滤+含CampaignTypes过滤(sponsoredProducts) — 7.4%
+TimeType=1+含CampaignTags过滤+无广告类型过滤 — 3.4%
+TimeType=3+无标签过滤+无广告类型过滤 — 3.0%
+TimeType=1+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 1.6%
+TimeType=0+无标签过滤+无广告类型过滤 — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007" ht="128" customHeight="1">
       <c r="A1007" s="41" t="n"/>
       <c r="B1007" s="23" t="inlineStr">
         <is>
@@ -35077,6 +35680,18 @@
       <c r="E1007" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1007" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=1+无标签过滤+无广告类型过滤 — 77.8%
+TimeType=1+无标签过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 8.4%
+TimeType=1+含CampaignTags过滤+无广告类型过滤 — 2.8%
+TimeType=3+无标签过滤+无广告类型过滤 — 2.6%
+TimeType=1+含CampaignTags过滤+含CampaignTypes过滤(sponsoredProducts,headlineSearch,sponsoredDisplay) — 1.8%
+TimeType=0+无标签过滤+无广告类型过滤 — 1.4%
+TimeType=3+无标签过滤+含CampaignTypes过滤(headlineSearch) — 1.0%
+TimeType=2+无标签过滤+无广告类型过滤 — 1.0%</t>
         </is>
       </c>
     </row>
@@ -36375,7 +36990,7 @@
         </is>
       </c>
     </row>
-    <row r="1057">
+    <row r="1057" ht="16" customHeight="1">
       <c r="A1057" s="41" t="n"/>
       <c r="B1057" s="24" t="inlineStr">
         <is>
@@ -36397,8 +37012,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1058">
+      <c r="F1057" s="44" t="inlineStr">
+        <is>
+          <t>应用单个负向Item到Amazon广告组(含后置清理,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058" ht="32" customHeight="1">
       <c r="A1058" s="41" t="n"/>
       <c r="B1058" s="27" t="inlineStr">
         <is>
@@ -36420,8 +37040,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1059">
+      <c r="F1058" s="44" t="inlineStr">
+        <is>
+          <t>应用单个Item(按ItemId,含后置清理,可重复) — 90%
+批量应用多个Item(按ItemIds,含后置清理,可重复) — 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059" ht="16" customHeight="1">
       <c r="A1059" s="41" t="n"/>
       <c r="B1059" s="23" t="inlineStr">
         <is>
@@ -36443,8 +37069,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1060">
+      <c r="F1059" s="44" t="inlineStr">
+        <is>
+          <t>批量对列表追加真实ASIN(含后置清理,可重复) — 12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060" ht="64" customHeight="1">
       <c r="A1060" s="41" t="n"/>
       <c r="B1060" s="27" t="inlineStr">
         <is>
@@ -36466,8 +37097,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1061">
+      <c r="F1060" s="44" t="inlineStr">
+        <is>
+          <t>adgroup级product类型负向列表(含后置清理,可重复) — 50.0%
+campaign级product类型负向列表(含后置清理,可重复) — 25.0%
+adgroup级brand类型负向列表(含后置清理,可重复) — 20.8%
+未指定Level的product类型负向列表(含后置清理,可重复) — 4.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061" ht="64" customHeight="1">
       <c r="A1061" s="41" t="n"/>
       <c r="B1061" s="23" t="inlineStr">
         <is>
@@ -36489,8 +37128,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1062">
+      <c r="F1061" s="44" t="inlineStr">
+        <is>
+          <t>按CampaignTag应用到adgroup级(含后置清理,可重复) — 69.6%
+按CampaignTag应用到campaign级(含后置清理,可重复) — 12.3%
+直接指定campaign应用到campaign级(含后置清理,可重复) — 11.6%
+直接指定adgroup应用到adgroup级(含后置清理,可重复) — 6.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062" ht="48" customHeight="1">
       <c r="A1062" s="41" t="n"/>
       <c r="B1062" s="27" t="inlineStr">
         <is>
@@ -36512,8 +37159,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1063">
+      <c r="F1062" s="44" t="inlineStr">
+        <is>
+          <t>大批量ASIN(含后置清理,可重复) — 64.6%
+少量ASIN(含后置清理,可重复) — 24.2%
+中等批量品牌名(含后置清理,可重复) — 11.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063" ht="16" customHeight="1">
       <c r="A1063" s="41" t="n"/>
       <c r="B1063" s="23" t="inlineStr">
         <is>
@@ -36535,8 +37189,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1064">
+      <c r="F1063" s="44" t="inlineStr">
+        <is>
+          <t>按id删除负向列表(前置自建,可重复) — 78.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064" ht="32" customHeight="1">
       <c r="A1064" s="41" t="n"/>
       <c r="B1064" s="27" t="inlineStr">
         <is>
@@ -36558,8 +37217,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1065">
+      <c r="F1064" s="44" t="inlineStr">
+        <is>
+          <t>archieveDelete归档删除PAT(前置自建+可重复) — 54.5%
+delete硬删除PAT(前置自建+可重复) — 31.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065" ht="16" customHeight="1">
       <c r="A1065" s="41" t="n"/>
       <c r="B1065" s="23" t="inlineStr">
         <is>
@@ -36581,8 +37246,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1066">
+      <c r="F1065" s="44" t="inlineStr">
+        <is>
+          <t>按Id查询负向列表详情 — 98.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066" ht="16" customHeight="1">
       <c r="A1066" s="41" t="n"/>
       <c r="B1066" s="27" t="inlineStr">
         <is>
@@ -36604,8 +37274,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1067">
+      <c r="F1066" s="44" t="inlineStr">
+        <is>
+          <t>查询单个item应用状态 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067" ht="16" customHeight="1">
       <c r="A1067" s="41" t="n"/>
       <c r="B1067" s="23" t="inlineStr">
         <is>
@@ -36627,8 +37302,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1068">
+      <c r="F1067" s="44" t="inlineStr">
+        <is>
+          <t>按列表Id查询PAT明细表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068" ht="16" customHeight="1">
       <c r="A1068" s="41" t="n"/>
       <c r="B1068" s="27" t="inlineStr">
         <is>
@@ -36650,8 +37330,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1069">
+      <c r="F1068" s="44" t="inlineStr">
+        <is>
+          <t>按profileIds过滤查询负向列表 — 17.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069" ht="16" customHeight="1">
       <c r="A1069" s="41" t="n"/>
       <c r="B1069" s="23" t="inlineStr">
         <is>
@@ -36671,6 +37356,11 @@
       <c r="E1069" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1069" s="44" t="inlineStr">
+        <is>
+          <t>修改负向列表名称(前置自建+后置清理,可重复) — 88.9%</t>
         </is>
       </c>
     </row>
@@ -37409,7 +38099,7 @@
         </is>
       </c>
     </row>
-    <row r="1097">
+    <row r="1097" ht="48" customHeight="1">
       <c r="A1097" s="41" t="n"/>
       <c r="B1097" s="24" t="inlineStr">
         <is>
@@ -37431,8 +38121,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1098">
+      <c r="F1097" s="44" t="inlineStr">
+        <is>
+          <t>场景1:仅确认不新建绑定(0个profile) — 50.8%
+场景2:确认绑定单个profile — 21.6%
+场景3:确认绑定多个profile — 27.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098" ht="64" customHeight="1">
       <c r="A1098" s="41" t="n"/>
       <c r="B1098" s="27" t="inlineStr">
         <is>
@@ -37454,8 +38151,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1099">
+      <c r="F1098" s="44" t="inlineStr">
+        <is>
+          <t>场景1:主站product.pacvue.com授权回调 — 73.0%
+场景2:amazon-dsp子路径授权回调 — 21.2%
+场景3:groupm.pacvue.com租户回调 — 3.0%
+场景4:ec.ca-parade.jp日本租户回调 — 2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099" ht="16" customHeight="1">
       <c r="A1099" s="41" t="n"/>
       <c r="B1099" s="23" t="inlineStr">
         <is>
@@ -37477,8 +38182,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1100">
+      <c r="F1099" s="44" t="inlineStr">
+        <is>
+          <t>场景1:Google登录授权回调(无ES样本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100" ht="16" customHeight="1">
       <c r="A1100" s="41" t="n"/>
       <c r="B1100" s="27" t="inlineStr">
         <is>
@@ -37500,8 +38210,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1101">
+      <c r="F1100" s="44" t="inlineStr">
+        <is>
+          <t>场景1:通用授权回调(无ES样本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101" ht="16" customHeight="1">
       <c r="A1101" s="41" t="n"/>
       <c r="B1101" s="23" t="inlineStr">
         <is>
@@ -37523,8 +38238,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1102">
+      <c r="F1101" s="44" t="inlineStr">
+        <is>
+          <t>场景1:测试重定向(无ES样本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102" ht="16" customHeight="1">
       <c r="A1102" s="41" t="n"/>
       <c r="B1102" s="27" t="inlineStr">
         <is>
@@ -37546,8 +38266,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1103">
+      <c r="F1102" s="44" t="inlineStr">
+        <is>
+          <t>场景1:测试Profile重定向(无ES样本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103" ht="112" customHeight="1">
       <c r="A1103" s="41" t="n"/>
       <c r="B1103" s="23" t="inlineStr">
         <is>
@@ -37567,6 +38292,17 @@
       <c r="E1103" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1103" s="44" t="inlineStr">
+        <is>
+          <t>场景1:US卖家/供应商回调 — 63.8%
+场景2:JP卖家/供应商回调 — 22.4%
+场景3:IN卖家/供应商回调 — 4.0%
+场景4:DE卖家/供应商回调 — 2.6%
+场景5:UK卖家/供应商回调 — 2.2%
+场景6:CA卖家/供应商回调 — 1.2%
+场景7:MX卖家/供应商回调 — 1.0%</t>
         </is>
       </c>
     </row>
@@ -37621,7 +38357,7 @@
         </is>
       </c>
     </row>
-    <row r="1106">
+    <row r="1106" ht="16" customHeight="1">
       <c r="A1106" s="41" t="n"/>
       <c r="B1106" s="26" t="inlineStr">
         <is>
@@ -37643,8 +38379,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1107">
+      <c r="F1106" s="44" t="inlineStr">
+        <is>
+          <t>场景1:单个广告活动加入Portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107" ht="48" customHeight="1">
       <c r="A1107" s="41" t="n"/>
       <c r="B1107" s="23" t="inlineStr">
         <is>
@@ -37666,8 +38407,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1108">
+      <c r="F1107" s="44" t="inlineStr">
+        <is>
+          <t>场景1:单个Portfolio仅改名(不涉及预算/状态) — 68.8%
+场景2:批量更新多个Portfolio的预算+预算共享控制+启用状态 — 28.9%
+场景3:批量重命名多个Portfolio(不涉及预算/状态) — 2.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108" ht="64" customHeight="1">
       <c r="A1108" s="41" t="n"/>
       <c r="B1108" s="27" t="inlineStr">
         <is>
@@ -37689,8 +38437,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1109">
+      <c r="F1108" s="44" t="inlineStr">
+        <is>
+          <t>场景1:仅名称+启用状态(无预算无预算控制)(含后置清理,可重复) — 50.8%
+场景2:名称+启用状态+预算共享控制(无预算)(含后置清理,可重复) — 22.4%
+场景3:名称+启用状态+日期区间预算+预算共享控制(含后置清理,可重复) — 16.6%
+场景4:名称+启用状态+不限预算(NO CAP)(含后置清理,可重复) — 6.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109" ht="16" customHeight="1">
       <c r="A1109" s="41" t="n"/>
       <c r="B1109" s="23" t="inlineStr">
         <is>
@@ -37710,6 +38466,11 @@
       <c r="E1109" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1109" s="44" t="inlineStr">
+        <is>
+          <t>场景1:单个Portfolio设置预算+预算共享控制+启用状态 — 99.6%</t>
         </is>
       </c>
     </row>
@@ -37915,7 +38676,7 @@
         </is>
       </c>
     </row>
-    <row r="1117">
+    <row r="1117" ht="64" customHeight="1">
       <c r="A1117" s="41" t="n"/>
       <c r="B1117" s="24" t="inlineStr">
         <is>
@@ -37937,8 +38698,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1118">
+      <c r="F1117" s="44" t="inlineStr">
+        <is>
+          <t>单ASIN无SKU查询 — 38.3%
+单ASIN带SKU查询 — 15.2%
+多ASIN(2个)批量查询 — 15.9%
+大批量ASIN(100个)查询 — 2.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118" ht="16" customHeight="1">
       <c r="A1118" s="41" t="n"/>
       <c r="B1118" s="27" t="inlineStr">
         <is>
@@ -37960,8 +38729,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1119">
+      <c r="F1118" s="44" t="inlineStr">
+        <is>
+          <t>当前周期vs对比周期曝光下降查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119" ht="48" customHeight="1">
       <c r="A1119" s="41" t="n"/>
       <c r="B1119" s="23" t="inlineStr">
         <is>
@@ -37983,8 +38757,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1120">
+      <c r="F1119" s="44" t="inlineStr">
+        <is>
+          <t>多Profile(&gt;=10个)销售占比查询 — 66.7%
+少量Profile(2-9个)销售占比查询 — 26.7%
+单Profile销售占比查询 — 6.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120" ht="32" customHeight="1">
       <c r="A1120" s="41" t="n"/>
       <c r="B1120" s="27" t="inlineStr">
         <is>
@@ -38004,6 +38785,12 @@
       <c r="E1120" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1120" s="44" t="inlineStr">
+        <is>
+          <t>不带搜索词分页查询 — 92.1%
+按ASIN关键字搜索 — 7.9%</t>
         </is>
       </c>
     </row>
@@ -38142,7 +38929,7 @@
         </is>
       </c>
     </row>
-    <row r="1126">
+    <row r="1126" ht="16" customHeight="1">
       <c r="A1126" s="41" t="n"/>
       <c r="B1126" s="26" t="inlineStr">
         <is>
@@ -38164,8 +38951,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1127">
+      <c r="F1126" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按店铺名批量添加追踪ASIN(含后置清理,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127" ht="32" customHeight="1">
       <c r="A1127" s="41" t="n"/>
       <c r="B1127" s="23" t="inlineStr">
         <is>
@@ -38187,8 +38979,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1128">
+      <c r="F1127" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单ASIN添加追踪(含后置清理,可重复) — 75.0%
+场景2: 批量ASIN添加追踪(逗号拼接,含后置清理,可重复) — 25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128" ht="32" customHeight="1">
       <c r="A1128" s="41" t="n"/>
       <c r="B1128" s="27" t="inlineStr">
         <is>
@@ -38210,8 +39008,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1129">
+      <c r="F1128" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 无关键词分页浏览追踪列表 — 81.2%
+场景2: 按关键词搜索追踪ASIN — 18.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129" ht="16" customHeight="1">
       <c r="A1129" s="41" t="n"/>
       <c r="B1129" s="23" t="inlineStr">
         <is>
@@ -38233,8 +39037,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1130">
+      <c r="F1129" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按日期区间查看追踪ASIN详情(含前置创建与后置清理,可重复) — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130" ht="16" customHeight="1">
       <c r="A1130" s="41" t="n"/>
       <c r="B1130" s="27" t="inlineStr">
         <is>
@@ -38256,8 +39065,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1131">
+      <c r="F1130" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 查看ASIN卖家信息 — 74.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131" ht="48" customHeight="1">
       <c r="A1131" s="41" t="n"/>
       <c r="B1131" s="23" t="inlineStr">
         <is>
@@ -38277,6 +39091,13 @@
       <c r="E1131" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1131" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单个追踪ASIN归档(含前置创建,可重复) — 46.5%
+场景2: 批量追踪ASIN归档(含前置创建,可重复) — 27.9%
+场景3: 单个追踪ASIN暂停(含前置创建与后置归档清理,可重复) — 2.3%</t>
         </is>
       </c>
     </row>
@@ -38631,7 +39452,7 @@
         </is>
       </c>
     </row>
-    <row r="1144">
+    <row r="1144" ht="16" customHeight="1">
       <c r="A1144" s="41" t="n"/>
       <c r="B1144" s="26" t="inlineStr">
         <is>
@@ -38653,8 +39474,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1145">
+      <c r="F1144" s="44" t="inlineStr">
+        <is>
+          <t>下载AdGroup关键词研究表格 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145" ht="16" customHeight="1">
       <c r="A1145" s="41" t="n"/>
       <c r="B1145" s="23" t="inlineStr">
         <is>
@@ -38676,8 +39502,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1146">
+      <c r="F1145" s="44" t="inlineStr">
+        <is>
+          <t>下载Asin关键词研究表格 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146" ht="16" customHeight="1">
       <c r="A1146" s="41" t="n"/>
       <c r="B1146" s="27" t="inlineStr">
         <is>
@@ -38699,8 +39530,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1147">
+      <c r="F1146" s="44" t="inlineStr">
+        <is>
+          <t>下载H10 PAT研究表格</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147" ht="16" customHeight="1">
       <c r="A1147" s="41" t="n"/>
       <c r="B1147" s="23" t="inlineStr">
         <is>
@@ -38722,8 +39558,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1148">
+      <c r="F1147" s="44" t="inlineStr">
+        <is>
+          <t>下载Keyword关键词研究表格 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148" ht="16" customHeight="1">
       <c r="A1148" s="41" t="n"/>
       <c r="B1148" s="27" t="inlineStr">
         <is>
@@ -38745,8 +39586,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1149">
+      <c r="F1148" s="44" t="inlineStr">
+        <is>
+          <t>下载搜索词趋势图表数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149" ht="16" customHeight="1">
       <c r="A1149" s="41" t="n"/>
       <c r="B1149" s="23" t="inlineStr">
         <is>
@@ -38768,8 +39614,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1150">
+      <c r="F1149" s="44" t="inlineStr">
+        <is>
+          <t>导出Research页面数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150" ht="48" customHeight="1">
       <c r="A1150" s="41" t="n"/>
       <c r="B1150" s="27" t="inlineStr">
         <is>
@@ -38791,8 +39642,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1151">
+      <c r="F1150" s="44" t="inlineStr">
+        <is>
+          <t>按转化排序获取AdGroup更多关键词H10数据 — 44%
+按点击排序获取AdGroup更多关键词H10数据 — 37.4%
+不指定排序方式获取AdGroup更多关键词H10数据 — 18.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151" ht="32" customHeight="1">
       <c r="A1151" s="41" t="n"/>
       <c r="B1151" s="23" t="inlineStr">
         <is>
@@ -38814,8 +39672,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1152">
+      <c r="F1151" s="44" t="inlineStr">
+        <is>
+          <t>按转化排序获取Asin关键词列表 — 64.5%
+按点击排序获取Asin关键词列表 — 31.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152" ht="32" customHeight="1">
       <c r="A1152" s="41" t="n"/>
       <c r="B1152" s="27" t="inlineStr">
         <is>
@@ -38837,8 +39701,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1153">
+      <c r="F1152" s="44" t="inlineStr">
+        <is>
+          <t>单Asin获取更多关键词 — 81.4%
+多Asin获取更多关键词 — 18.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153" ht="32" customHeight="1">
       <c r="A1153" s="41" t="n"/>
       <c r="B1153" s="23" t="inlineStr">
         <is>
@@ -38860,8 +39730,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1154">
+      <c r="F1153" s="44" t="inlineStr">
+        <is>
+          <t>按Asin列表获取SB关键词 — 73%
+按Store页面URL获取SB关键词 — 27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154" ht="16" customHeight="1">
       <c r="A1154" s="41" t="n"/>
       <c r="B1154" s="27" t="inlineStr">
         <is>
@@ -38883,8 +39759,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1155">
+      <c r="F1154" s="44" t="inlineStr">
+        <is>
+          <t>获取禁用Asin列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155" ht="16" customHeight="1">
       <c r="A1155" s="41" t="n"/>
       <c r="B1155" s="23" t="inlineStr">
         <is>
@@ -38906,8 +39787,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1156">
+      <c r="F1155" s="44" t="inlineStr">
+        <is>
+          <t>获取图表默认Asin参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156" ht="16" customHeight="1">
       <c r="A1156" s="41" t="n"/>
       <c r="B1156" s="27" t="inlineStr">
         <is>
@@ -38929,8 +39815,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1157">
+      <c r="F1156" s="44" t="inlineStr">
+        <is>
+          <t>获取关键词H10数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157" ht="16" customHeight="1">
       <c r="A1157" s="41" t="n"/>
       <c r="B1157" s="23" t="inlineStr">
         <is>
@@ -38952,8 +39843,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1158">
+      <c r="F1157" s="44" t="inlineStr">
+        <is>
+          <t>获取H10黑盒过滤关键词数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158" ht="32" customHeight="1">
       <c r="A1158" s="41" t="n"/>
       <c r="B1158" s="27" t="inlineStr">
         <is>
@@ -38975,8 +39871,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1159">
+      <c r="F1158" s="44" t="inlineStr">
+        <is>
+          <t>查询关键词无出价标记(未指定Campaign/AdGroup) — 93.4%
+查询关键词无出价标记(指定Campaign/AdGroup) — 6.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159" ht="16" customHeight="1">
       <c r="A1159" s="41" t="n"/>
       <c r="B1159" s="23" t="inlineStr">
         <is>
@@ -38998,8 +39900,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1160">
+      <c r="F1159" s="44" t="inlineStr">
+        <is>
+          <t>H10 PAT研究(ASIN对ASIN推荐) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160" ht="48" customHeight="1">
       <c r="A1160" s="41" t="n"/>
       <c r="B1160" s="27" t="inlineStr">
         <is>
@@ -39021,8 +39928,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1161">
+      <c r="F1160" s="44" t="inlineStr">
+        <is>
+          <t>H10建议(关键词对关键词) — 86%
+H10建议(Asin对关键词) — 12.4%
+H10建议(Asin对Asin) — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161" ht="16" customHeight="1">
       <c r="A1161" s="41" t="n"/>
       <c r="B1161" s="23" t="inlineStr">
         <is>
@@ -39042,6 +39956,11 @@
       <c r="E1161" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1161" s="44" t="inlineStr">
+        <is>
+          <t>获取搜索词趋势图表数据</t>
         </is>
       </c>
     </row>
@@ -39785,7 +40704,7 @@
         </is>
       </c>
     </row>
-    <row r="1188">
+    <row r="1188" ht="16" customHeight="1">
       <c r="A1188" s="41" t="n"/>
       <c r="B1188" s="26" t="inlineStr">
         <is>
@@ -39807,8 +40726,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1189">
+      <c r="F1188" s="44" t="inlineStr">
+        <is>
+          <t>无参数获取PacvueUniversity跳转链接 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189" ht="16" customHeight="1">
       <c r="A1189" s="41" t="n"/>
       <c r="B1189" s="23" t="inlineStr">
         <is>
@@ -39828,6 +40752,11 @@
       <c r="E1189" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1189" s="44" t="inlineStr">
+        <is>
+          <t>无参数获取Zendesk跳转链接 — 100%</t>
         </is>
       </c>
     </row>
@@ -40148,7 +41077,7 @@
         </is>
       </c>
     </row>
-    <row r="1201">
+    <row r="1201" ht="48" customHeight="1">
       <c r="A1201" s="41" t="n"/>
       <c r="B1201" s="24" t="inlineStr">
         <is>
@@ -40170,8 +41099,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1202">
+      <c r="F1201" s="44" t="inlineStr">
+        <is>
+          <t>查询vendor未绑定profile状态 — 51.2%
+绑定vendor到广告Profile — 28.6%
+空数组请求 — 20.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202" ht="16" customHeight="1">
       <c r="A1202" s="41" t="n"/>
       <c r="B1202" s="27" t="inlineStr">
         <is>
@@ -40193,8 +41129,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1203">
+      <c r="F1202" s="44" t="inlineStr">
+        <is>
+          <t>查询用户已选widget列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203" ht="16" customHeight="1">
       <c r="A1203" s="41" t="n"/>
       <c r="B1203" s="23" t="inlineStr">
         <is>
@@ -40216,8 +41157,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1204">
+      <c r="F1203" s="44" t="inlineStr">
+        <is>
+          <t>查询用户偏好设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204" ht="32" customHeight="1">
       <c r="A1204" s="41" t="n"/>
       <c r="B1204" s="27" t="inlineStr">
         <is>
@@ -40239,8 +41185,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1205">
+      <c r="F1204" s="44" t="inlineStr">
+        <is>
+          <t>空VendorId查询 — 63.8%
+按真实VendorId查询绑定情况 — 36.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205" ht="16" customHeight="1">
       <c r="A1205" s="41" t="n"/>
       <c r="B1205" s="23" t="inlineStr">
         <is>
@@ -40262,8 +41214,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1206">
+      <c r="F1205" s="44" t="inlineStr">
+        <is>
+          <t>查询Amazon授权状态 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206" ht="16" customHeight="1">
       <c r="A1206" s="41" t="n"/>
       <c r="B1206" s="27" t="inlineStr">
         <is>
@@ -40285,8 +41242,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1207">
+      <c r="F1206" s="44" t="inlineStr">
+        <is>
+          <t>保存用户widget偏好</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207" ht="32" customHeight="1">
       <c r="A1207" s="41" t="n"/>
       <c r="B1207" s="23" t="inlineStr">
         <is>
@@ -40308,8 +41270,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1208">
+      <c r="F1207" s="44" t="inlineStr">
+        <is>
+          <t>保存vendor绑定关系(含Profile) — 93.75%
+保存vendor绑定关系(Profiles为空) — 6.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208" ht="16" customHeight="1">
       <c r="A1208" s="41" t="n"/>
       <c r="B1208" s="27" t="inlineStr">
         <is>
@@ -40329,6 +41297,11 @@
       <c r="E1208" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1208" s="44" t="inlineStr">
+        <is>
+          <t>更新用户偏好设置</t>
         </is>
       </c>
     </row>
@@ -40702,7 +41675,7 @@
         </is>
       </c>
     </row>
-    <row r="1224">
+    <row r="1224" ht="80" customHeight="1">
       <c r="A1224" s="41" t="n"/>
       <c r="B1224" s="26" t="inlineStr">
         <is>
@@ -40724,8 +41697,17 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1225">
+      <c r="F1224" s="44" t="inlineStr">
+        <is>
+          <t>SB视频广告素材预审核 — 38.6%
+SB图片Logo预审核 — 31.8%
+SD图片Logo预审核 — 22.0%
+STV视频预审核 — 3.8%
+SB视频广告图片Logo预审核 — 2.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225" ht="80" customHeight="1">
       <c r="A1225" s="41" t="n"/>
       <c r="B1225" s="23" t="inlineStr">
         <is>
@@ -40747,8 +41729,17 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1226">
+      <c r="F1225" s="44" t="inlineStr">
+        <is>
+          <t>按assertId预审核SB图片素材 — 68.3%
+按assertId预审核SB视频广告图片Logo — 16.5%
+按assertId预审核SD视频 — 6.1%
+按assertId预审核SD图片Logo — 4.9%
+按assertId预审核SB Spotlight图片Logo — 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226" ht="16" customHeight="1">
       <c r="A1226" s="41" t="n"/>
       <c r="B1226" s="27" t="inlineStr">
         <is>
@@ -40770,8 +41761,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1227">
+      <c r="F1226" s="44" t="inlineStr">
+        <is>
+          <t>查询SB广告活动出价调整 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227" ht="64" customHeight="1">
       <c r="A1227" s="41" t="n"/>
       <c r="B1227" s="23" t="inlineStr">
         <is>
@@ -40793,8 +41789,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1228">
+      <c r="F1227" s="44" t="inlineStr">
+        <is>
+          <t>3个ASIN生成SB标题推荐 — 65.0%
+单ASIN生成SB标题推荐 — 30.6%
+2个ASIN生成SB标题推荐 — 2.6%
+Spotlight+StorePages生成标题推荐 — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228" ht="16" customHeight="1">
       <c r="A1228" s="41" t="n"/>
       <c r="B1228" s="27" t="inlineStr">
         <is>
@@ -40816,8 +41820,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1229">
+      <c r="F1228" s="44" t="inlineStr">
+        <is>
+          <t>查询SB商品定向类目树</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229" ht="16" customHeight="1">
       <c r="A1229" s="41" t="n"/>
       <c r="B1229" s="23" t="inlineStr">
         <is>
@@ -40839,8 +41848,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1230">
+      <c r="F1229" s="44" t="inlineStr">
+        <is>
+          <t>查询指定类目的细化定向条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230" ht="16" customHeight="1">
       <c r="A1230" s="41" t="n"/>
       <c r="B1230" s="27" t="inlineStr">
         <is>
@@ -40862,8 +41876,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1231">
+      <c r="F1230" s="44" t="inlineStr">
+        <is>
+          <t>按类目查询商品定向匹配数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231" ht="16" customHeight="1">
       <c r="A1231" s="41" t="n"/>
       <c r="B1231" s="23" t="inlineStr">
         <is>
@@ -40883,6 +41902,11 @@
       <c r="E1231" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1231" s="44" t="inlineStr">
+        <is>
+          <t>按落地页ASIN查询成本控制推荐值</t>
         </is>
       </c>
     </row>
@@ -41313,7 +42337,7 @@
         </is>
       </c>
     </row>
-    <row r="1247">
+    <row r="1247" ht="16" customHeight="1">
       <c r="A1247" s="41" t="n"/>
       <c r="B1247" s="24" t="inlineStr">
         <is>
@@ -41335,8 +42359,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1248">
+      <c r="F1247" s="44" t="inlineStr">
+        <is>
+          <t>批量更新多个广告组下创意的标题文案 — 44.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248" ht="16" customHeight="1">
       <c r="A1248" s="41" t="n"/>
       <c r="B1248" s="27" t="inlineStr">
         <is>
@@ -41358,8 +42387,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1249">
+      <c r="F1248" s="44" t="inlineStr">
+        <is>
+          <t>单图片创意(横/方/竖图)在现有广告组下新建 — 38.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249" ht="16" customHeight="1">
       <c r="A1249" s="41" t="n"/>
       <c r="B1249" s="23" t="inlineStr">
         <is>
@@ -41381,8 +42415,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1250">
+      <c r="F1249" s="44" t="inlineStr">
+        <is>
+          <t>单profile+日期范围查询渠道广告表现 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250" ht="16" customHeight="1">
       <c r="A1250" s="41" t="n"/>
       <c r="B1250" s="27" t="inlineStr">
         <is>
@@ -41404,8 +42443,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1251">
+      <c r="F1250" s="44" t="inlineStr">
+        <is>
+          <t>按天分组查询曝光效率图表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251" ht="16" customHeight="1">
       <c r="A1251" s="41" t="n"/>
       <c r="B1251" s="23" t="inlineStr">
         <is>
@@ -41427,8 +42471,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1252">
+      <c r="F1251" s="44" t="inlineStr">
+        <is>
+          <t>单profile+日期范围查询曝光效率看板 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252" ht="16" customHeight="1">
       <c r="A1252" s="41" t="n"/>
       <c r="B1252" s="27" t="inlineStr">
         <is>
@@ -41450,8 +42499,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1253">
+      <c r="F1252" s="44" t="inlineStr">
+        <is>
+          <t>单profile+日期范围查询月度广告类型表现 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253" ht="16" customHeight="1">
       <c r="A1253" s="41" t="n"/>
       <c r="B1253" s="23" t="inlineStr">
         <is>
@@ -41473,8 +42527,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1254">
+      <c r="F1253" s="44" t="inlineStr">
+        <is>
+          <t>单profile+日期范围+分页查询商品表现 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254" ht="16" customHeight="1">
       <c r="A1254" s="41" t="n"/>
       <c r="B1254" s="27" t="inlineStr">
         <is>
@@ -41496,8 +42555,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1255">
+      <c r="F1254" s="44" t="inlineStr">
+        <is>
+          <t>单profile+日期范围查询推荐ASIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255" ht="16" customHeight="1">
       <c r="A1255" s="41" t="n"/>
       <c r="B1255" s="23" t="inlineStr">
         <is>
@@ -41519,8 +42583,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1256">
+      <c r="F1255" s="44" t="inlineStr">
+        <is>
+          <t>单profile+日期范围+按花费排序分页查询SD广告活动数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256" ht="16" customHeight="1">
       <c r="A1256" s="41" t="n"/>
       <c r="B1256" s="27" t="inlineStr">
         <is>
@@ -41542,8 +42611,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1257">
+      <c r="F1256" s="44" t="inlineStr">
+        <is>
+          <t>按广告组ID列表查询SD创意 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257" ht="16" customHeight="1">
       <c r="A1257" s="41" t="n"/>
       <c r="B1257" s="23" t="inlineStr">
         <is>
@@ -41565,8 +42639,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1258">
+      <c r="F1257" s="44" t="inlineStr">
+        <is>
+          <t>按profile查询建议投放商品 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258" ht="16" customHeight="1">
       <c r="A1258" s="41" t="n"/>
       <c r="B1258" s="27" t="inlineStr">
         <is>
@@ -41588,8 +42667,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1259">
+      <c r="F1258" s="44" t="inlineStr">
+        <is>
+          <t>按profile查询SD广告组列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259" ht="16" customHeight="1">
       <c r="A1259" s="41" t="n"/>
       <c r="B1259" s="23" t="inlineStr">
         <is>
@@ -41611,8 +42695,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1260">
+      <c r="F1259" s="44" t="inlineStr">
+        <is>
+          <t>单profile+日期范围查询定向对比数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260" ht="16" customHeight="1">
       <c r="A1260" s="41" t="n"/>
       <c r="B1260" s="27" t="inlineStr">
         <is>
@@ -41634,8 +42723,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1261">
+      <c r="F1260" s="44" t="inlineStr">
+        <is>
+          <t>更新已有创意的标题文案(headline) — 36.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261" ht="16" customHeight="1">
       <c r="A1261" s="41" t="n"/>
       <c r="B1261" s="24" t="inlineStr">
         <is>
@@ -41657,8 +42751,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1262">
+      <c r="F1261" s="44" t="inlineStr">
+        <is>
+          <t>在现有广告组下新建广告(结构占位,待补真实值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262" ht="16" customHeight="1">
       <c r="A1262" s="41" t="n"/>
       <c r="B1262" s="27" t="inlineStr">
         <is>
@@ -41680,8 +42779,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1263">
+      <c r="F1262" s="44" t="inlineStr">
+        <is>
+          <t>在现有活动下新建暂停状态的广告组(点击优化+图片创意) — 20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263" ht="16" customHeight="1">
       <c r="A1263" s="41" t="n"/>
       <c r="B1263" s="23" t="inlineStr">
         <is>
@@ -41703,8 +42807,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1264">
+      <c r="F1263" s="44" t="inlineStr">
+        <is>
+          <t>同账号内复制活动(不复制创意)并保持暂停状态 — 18.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264" ht="16" customHeight="1">
       <c r="A1264" s="41" t="n"/>
       <c r="B1264" s="27" t="inlineStr">
         <is>
@@ -41726,8 +42835,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1265">
+      <c r="F1264" s="44" t="inlineStr">
+        <is>
+          <t>同账号内复制活动及广告组ASIN(含创意)并保持暂停状态 — 41.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265" ht="16" customHeight="1">
       <c r="A1265" s="41" t="n"/>
       <c r="B1265" s="23" t="inlineStr">
         <is>
@@ -41747,6 +42861,11 @@
       <c r="E1265" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1265" s="44" t="inlineStr">
+        <is>
+          <t>CPC计费+图片创意+新建广告组的完整活动创建(暂停状态) — 27.6%</t>
         </is>
       </c>
     </row>
@@ -41946,7 +43065,7 @@
         </is>
       </c>
     </row>
-    <row r="1273">
+    <row r="1273" ht="16" customHeight="1">
       <c r="A1273" s="41" t="n"/>
       <c r="B1273" s="24" t="inlineStr">
         <is>
@@ -41968,8 +43087,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1274">
+      <c r="F1273" s="44" t="inlineStr">
+        <is>
+          <t>查询广告组创意审核违规</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274" ht="64" customHeight="1">
       <c r="A1274" s="41" t="n"/>
       <c r="B1274" s="27" t="inlineStr">
         <is>
@@ -41991,8 +43115,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1275">
+      <c r="F1274" s="44" t="inlineStr">
+        <is>
+          <t>内容分类定向(contentCategorySimilarTo) — 48.6%
+受众定向(AUDIENCE SAME AS INTEREST等) — 40.5%
+商品分类+内容分类混合定向 — 8.1%
+单独商品分类定向(asinCategorySimilarTo) — 2.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275" ht="16" customHeight="1">
       <c r="A1275" s="41" t="n"/>
       <c r="B1275" s="23" t="inlineStr">
         <is>
@@ -42014,8 +43146,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1276">
+      <c r="F1275" s="44" t="inlineStr">
+        <is>
+          <t>查询创意审核政策违规</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276" ht="32" customHeight="1">
       <c r="A1276" s="41" t="n"/>
       <c r="B1276" s="27" t="inlineStr">
         <is>
@@ -42037,8 +43174,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1277">
+      <c r="F1276" s="44" t="inlineStr">
+        <is>
+          <t>单广告组查询(不含CreativeIds字段) — 92.6%
+单广告组查询(显式空CreativeIds数组) — 7.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277" ht="48" customHeight="1">
       <c r="A1277" s="41" t="n"/>
       <c r="B1277" s="23" t="inlineStr">
         <is>
@@ -42058,6 +43201,13 @@
       <c r="E1277" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1277" s="44" t="inlineStr">
+        <is>
+          <t>预览创意(PascalCase+真实Asin) — 50.4%
+预览创意(camelCase+真实Asin) — 45.9%
+预览创意(不指定Asin,仅按AssetId预览) — 3.8%</t>
         </is>
       </c>
     </row>
@@ -42429,7 +43579,7 @@
         </is>
       </c>
     </row>
-    <row r="1291">
+    <row r="1291" ht="16" customHeight="1">
       <c r="A1291" s="41" t="n"/>
       <c r="B1291" s="24" t="inlineStr">
         <is>
@@ -42451,8 +43601,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1292">
+      <c r="F1291" s="44" t="inlineStr">
+        <is>
+          <t>按keywordTagId查询关键词标签文本 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292" ht="32" customHeight="1">
       <c r="A1292" s="41" t="n"/>
       <c r="B1292" s="27" t="inlineStr">
         <is>
@@ -42474,8 +43629,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1293">
+      <c r="F1292" s="44" t="inlineStr">
+        <is>
+          <t>场景1:type=1按标签汇总透视报表 — 80%
+场景2:type=2按标签汇总透视报表 — 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293" ht="16" customHeight="1">
       <c r="A1293" s="41" t="n"/>
       <c r="B1293" s="23" t="inlineStr">
         <is>
@@ -42497,8 +43658,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1294">
+      <c r="F1293" s="44" t="inlineStr">
+        <is>
+          <t>查询全部标签树(不限profile) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294" ht="16" customHeight="1">
       <c r="A1294" s="41" t="n"/>
       <c r="B1294" s="27" t="inlineStr">
         <is>
@@ -42520,8 +43686,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1295">
+      <c r="F1294" s="44" t="inlineStr">
+        <is>
+          <t>下载标签透视报表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295" ht="16" customHeight="1">
       <c r="A1295" s="41" t="n"/>
       <c r="B1295" s="23" t="inlineStr">
         <is>
@@ -42541,6 +43712,11 @@
       <c r="E1295" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1295" s="44" t="inlineStr">
+        <is>
+          <t>按asinTagId查询ASIN列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -44692,7 +45868,7 @@
         </is>
       </c>
     </row>
-    <row r="1376">
+    <row r="1376" ht="16" customHeight="1">
       <c r="A1376" s="41" t="n"/>
       <c r="B1376" s="26" t="inlineStr">
         <is>
@@ -44712,6 +45888,11 @@
       <c r="E1376" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1376" s="44" t="inlineStr">
+        <is>
+          <t>空body调用</t>
         </is>
       </c>
     </row>
@@ -45277,7 +46458,7 @@
         </is>
       </c>
     </row>
-    <row r="1397">
+    <row r="1397" ht="16" customHeight="1">
       <c r="A1397" s="41" t="n"/>
       <c r="B1397" s="24" t="inlineStr">
         <is>
@@ -45299,8 +46480,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1398">
+      <c r="F1397" s="44" t="inlineStr">
+        <is>
+          <t>创建用户组(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398" ht="16" customHeight="1">
       <c r="A1398" s="41" t="n"/>
       <c r="B1398" s="27" t="inlineStr">
         <is>
@@ -45322,8 +46508,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1399">
+      <c r="F1398" s="44" t="inlineStr">
+        <is>
+          <t>删除用户组(含前置创建,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399" ht="16" customHeight="1">
       <c r="A1399" s="41" t="n"/>
       <c r="B1399" s="23" t="inlineStr">
         <is>
@@ -45345,8 +46536,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1400">
+      <c r="F1399" s="44" t="inlineStr">
+        <is>
+          <t>重命名用户组(含前置创建+后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400" ht="16" customHeight="1">
       <c r="A1400" s="41" t="n"/>
       <c r="B1400" s="27" t="inlineStr">
         <is>
@@ -45368,8 +46564,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="1401">
+      <c r="F1400" s="44" t="inlineStr">
+        <is>
+          <t>为用户组分配成员(含前置创建+后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401" ht="16" customHeight="1">
       <c r="A1401" s="41" t="n"/>
       <c r="B1401" s="23" t="inlineStr">
         <is>
@@ -45389,6 +46590,11 @@
       <c r="E1401" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F1401" s="44" t="inlineStr">
+        <is>
+          <t>查询当前账号全部用户组</t>
         </is>
       </c>
     </row>

--- a/single-api/mainapi/swagger_modules.xlsx
+++ b/single-api/mainapi/swagger_modules.xlsx
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F25" s="29" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G25" s="29" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="H25" s="29" t="inlineStr">
         <is>
-          <t>52% (14/27)</t>
+          <t>63% (17/27)</t>
         </is>
       </c>
     </row>
@@ -1844,16 +1844,16 @@
         </is>
       </c>
       <c r="F31" s="29" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>42% (5/12)</t>
+          <t>100% (12/12)</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2353,17 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>32</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="G46" s="29" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>89% (34/38)</t>
+      <c r="H46" s="29" t="inlineStr">
+        <is>
+          <t>97% (37/38)</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="F55" s="29" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>78% (7/9)</t>
+          <t>100% (9/9)</t>
         </is>
       </c>
     </row>
@@ -2761,15 +2761,15 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>4</v>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="29" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="29" t="inlineStr">
         <is>
           <t>100% (4/4)</t>
         </is>
@@ -2863,15 +2863,15 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="29" t="n">
         <v>385</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="29" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="29" t="inlineStr">
         <is>
           <t>100% (66/66)</t>
         </is>
@@ -2965,15 +2965,15 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="29" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="29" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
         </is>
@@ -10053,7 +10053,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="16" customHeight="1">
       <c r="A38" s="41" t="n"/>
       <c r="B38" s="27" t="inlineStr">
         <is>
@@ -10073,6 +10073,11 @@
       <c r="E38" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F38" s="44" t="inlineStr">
+        <is>
+          <t>校验用户名是否可用</t>
         </is>
       </c>
     </row>
@@ -10146,8 +10151,8 @@
       </c>
       <c r="F41" s="44" t="inlineStr">
         <is>
-          <t>isManaged=0 导出全部账号
-isManaged=1 导出已托管账号</t>
+          <t>isManaged=0 导出全部账号 — 85.7%
+isManaged=1 导出已托管账号 — 7.1%</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10203,7 @@
       </c>
       <c r="F43" s="44" t="inlineStr">
         <is>
-          <t>无参拉取管理者全部 Profile</t>
+          <t>无参拉取管理者全部 Profile — 98.2%</t>
         </is>
       </c>
     </row>
@@ -10226,8 +10231,8 @@
       </c>
       <c r="F44" s="44" t="inlineStr">
         <is>
-          <t>单个 advertiserId 查 3P Profile
-两个 advertiserId 查 3P Profile</t>
+          <t>单个 advertiserId 查 3P Profile — 89.0%
+两个 advertiserId 查 3P Profile — 6.0%</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10260,10 @@
       </c>
       <c r="F45" s="44" t="inlineStr">
         <is>
-          <t>amazon 查自己的 Profile 列表
-dsp 查自己的 Profile 列表
-dsp 仅 targetUserId 无 addedByUserId
-amazon 仅 targetUserId 无 addedByUserId</t>
+          <t>amazon 查自己的 Profile 列表 — 35.4%
+dsp 查自己的 Profile 列表 — 8.4%
+dsp 仅 targetUserId 无 addedByUserId — 9.8%
+amazon 仅 targetUserId 无 addedByUserId — 5.6%</t>
         </is>
       </c>
     </row>
@@ -10365,10 +10370,10 @@
       </c>
       <c r="F49" s="44" t="inlineStr">
         <is>
-          <t>US 市场托管日志
-CA 市场托管日志
-JP 市场托管日志
-UK 市场托管日志</t>
+          <t>US 市场托管日志 — 50.8%
+CA 市场托管日志 — 21.0%
+JP 市场托管日志 — 11.3%
+UK 市场托管日志 — 9.7%</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10406,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="16" customHeight="1">
       <c r="A51" s="41" t="n"/>
       <c r="B51" s="23" t="inlineStr">
         <is>
@@ -10421,6 +10426,11 @@
       <c r="E51" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F51" s="44" t="inlineStr">
+        <is>
+          <t>获取当前登录用户角色标志</t>
         </is>
       </c>
     </row>
@@ -10448,8 +10458,8 @@
       </c>
       <c r="F52" s="44" t="inlineStr">
         <is>
-          <t>仅 userId 查活动标签权限
-userId+时区 查活动标签权限</t>
+          <t>仅 userId 查活动标签权限 — 82.6%
+userId+时区 查活动标签权限 — 17.4%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10566,7 @@
       </c>
       <c r="F56" s="44" t="inlineStr">
         <is>
-          <t>取消托管后还原</t>
+          <t>取消托管后还原 — 68.8%</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10598,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="16" customHeight="1">
       <c r="A58" s="41" t="n"/>
       <c r="B58" s="27" t="inlineStr">
         <is>
@@ -10608,6 +10618,11 @@
       <c r="E58" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F58" s="44" t="inlineStr">
+        <is>
+          <t>设置用户角色为Staff</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12486,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="16" customHeight="1">
       <c r="A127" s="41" t="n"/>
       <c r="B127" s="24" t="inlineStr">
         <is>
@@ -12493,8 +12508,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="128">
+      <c r="F127" s="44" t="inlineStr">
+        <is>
+          <t>批量删除广告交易</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1">
       <c r="A128" s="41" t="n"/>
       <c r="B128" s="27" t="inlineStr">
         <is>
@@ -12516,8 +12536,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="129">
+      <c r="F128" s="44" t="inlineStr">
+        <is>
+          <t>创建广告交易(Deal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
       <c r="A129" s="41" t="n"/>
       <c r="B129" s="23" t="inlineStr">
         <is>
@@ -12539,8 +12564,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="130">
+      <c r="F129" s="44" t="inlineStr">
+        <is>
+          <t>创建广告交易并关联品牌关键词目标(含后置清理,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
       <c r="A130" s="41" t="n"/>
       <c r="B130" s="27" t="inlineStr">
         <is>
@@ -12562,8 +12592,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="131">
+      <c r="F130" s="44" t="inlineStr">
+        <is>
+          <t>单条创建广告交易目标(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
       <c r="A131" s="41" t="n"/>
       <c r="B131" s="23" t="inlineStr">
         <is>
@@ -12585,8 +12620,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="132">
+      <c r="F131" s="44" t="inlineStr">
+        <is>
+          <t>删除广告交易</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" s="41" t="n"/>
       <c r="B132" s="27" t="inlineStr">
         <is>
@@ -12606,6 +12646,11 @@
       <c r="E132" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F132" s="44" t="inlineStr">
+        <is>
+          <t>删除广告交易目标</t>
         </is>
       </c>
     </row>
@@ -12633,8 +12678,8 @@
       </c>
       <c r="F133" s="44" t="inlineStr">
         <is>
-          <t>5个品牌词约90天询价
-大批量54个关键词约30天询价</t>
+          <t>5个品牌词约90天询价 — 50%
+大批量54个关键词约30天询价 — 50%</t>
         </is>
       </c>
     </row>
@@ -12662,9 +12707,9 @@
       </c>
       <c r="F134" s="44" t="inlineStr">
         <is>
-          <t>单关键词预定校验
-3到4个品牌词批量校验
-大批量54个关键词校验</t>
+          <t>单关键词预定校验 — 42.9%
+3到4个品牌词批量校验 — 42.9%
+大批量54个关键词校验 — 14.3%</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12737,7 @@
       </c>
       <c r="F135" s="44" t="inlineStr">
         <is>
-          <t>拉取品牌词推荐</t>
+          <t>拉取品牌词推荐 — 98.1%</t>
         </is>
       </c>
     </row>
@@ -12752,7 +12797,7 @@
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="16" customHeight="1">
       <c r="A138" s="41" t="n"/>
       <c r="B138" s="27" t="inlineStr">
         <is>
@@ -12772,6 +12817,11 @@
       <c r="E138" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F138" s="44" t="inlineStr">
+        <is>
+          <t>更新广告交易</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18056,7 @@
         </is>
       </c>
     </row>
-    <row r="341">
+    <row r="341" ht="16" customHeight="1">
       <c r="A341" s="41" t="n"/>
       <c r="B341" s="24" t="inlineStr">
         <is>
@@ -18028,8 +18078,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="342">
+      <c r="F341" s="44" t="inlineStr">
+        <is>
+          <t>确认并执行广告组改名(含后置还原,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="16" customHeight="1">
       <c r="A342" s="41" t="n"/>
       <c r="B342" s="27" t="inlineStr">
         <is>
@@ -18051,8 +18106,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="343">
+      <c r="F342" s="44" t="inlineStr">
+        <is>
+          <t>确认并执行预算变更(含后置还原,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="16" customHeight="1">
       <c r="A343" s="41" t="n"/>
       <c r="B343" s="23" t="inlineStr">
         <is>
@@ -18074,8 +18134,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="344">
+      <c r="F343" s="44" t="inlineStr">
+        <is>
+          <t>确认并执行Campaign改名(含后置还原,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="16" customHeight="1">
       <c r="A344" s="41" t="n"/>
       <c r="B344" s="27" t="inlineStr">
         <is>
@@ -18097,8 +18162,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="345">
+      <c r="F344" s="44" t="inlineStr">
+        <is>
+          <t>确认并执行状态变更(含后置还原,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="16" customHeight="1">
       <c r="A345" s="41" t="n"/>
       <c r="B345" s="23" t="inlineStr">
         <is>
@@ -18120,8 +18190,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="346">
+      <c r="F345" s="44" t="inlineStr">
+        <is>
+          <t>确认并执行定向状态变更(含后置还原,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="32" customHeight="1">
       <c r="A346" s="41" t="n"/>
       <c r="B346" s="27" t="inlineStr">
         <is>
@@ -18143,8 +18218,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="347">
+      <c r="F346" s="44" t="inlineStr">
+        <is>
+          <t>确认并执行新建正向关键词定向(含后置归档,可重复)
+确认并执行新建否定关键词定向(含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="32" customHeight="1">
       <c r="A347" s="41" t="n"/>
       <c r="B347" s="23" t="inlineStr">
         <is>
@@ -18166,8 +18247,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="348">
+      <c r="F347" s="44" t="inlineStr">
+        <is>
+          <t>按广告组导出改名文件 — 93.3%
+仅按Campaign导出改名文件(不指定Adgroup) — 6.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="16" customHeight="1">
       <c r="A348" s="41" t="n"/>
       <c r="B348" s="27" t="inlineStr">
         <is>
@@ -18189,8 +18276,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="349">
+      <c r="F348" s="44" t="inlineStr">
+        <is>
+          <t>导出批量改名失败日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="16" customHeight="1">
       <c r="A349" s="41" t="n"/>
       <c r="B349" s="23" t="inlineStr">
         <is>
@@ -18212,8 +18304,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="350">
+      <c r="F349" s="44" t="inlineStr">
+        <is>
+          <t>按BatchId+KindType导出失败日志 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="16" customHeight="1">
       <c r="A350" s="41" t="n"/>
       <c r="B350" s="27" t="inlineStr">
         <is>
@@ -18235,8 +18332,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="351">
+      <c r="F350" s="44" t="inlineStr">
+        <is>
+          <t>按BatchId导出预算变更失败日志 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="16" customHeight="1">
       <c r="A351" s="41" t="n"/>
       <c r="B351" s="23" t="inlineStr">
         <is>
@@ -18258,8 +18360,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="352">
+      <c r="F351" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign导出预算变更文件 — 99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="16" customHeight="1">
       <c r="A352" s="41" t="n"/>
       <c r="B352" s="27" t="inlineStr">
         <is>
@@ -18281,8 +18388,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="353">
+      <c r="F352" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign导出改名文件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="16" customHeight="1">
       <c r="A353" s="41" t="n"/>
       <c r="B353" s="23" t="inlineStr">
         <is>
@@ -18304,8 +18416,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="354">
+      <c r="F353" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign导出状态变更文件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="16" customHeight="1">
       <c r="A354" s="41" t="n"/>
       <c r="B354" s="27" t="inlineStr">
         <is>
@@ -18327,8 +18444,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="355">
+      <c r="F354" s="44" t="inlineStr">
+        <is>
+          <t>按BatchId导出Campaign操作失败日志 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="16" customHeight="1">
       <c r="A355" s="41" t="n"/>
       <c r="B355" s="23" t="inlineStr">
         <is>
@@ -18350,8 +18472,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="356">
+      <c r="F355" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign+KindType导出创建定向文件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="32" customHeight="1">
       <c r="A356" s="41" t="n"/>
       <c r="B356" s="27" t="inlineStr">
         <is>
@@ -18373,8 +18500,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="357">
+      <c r="F356" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign+KindType+定向状态导出变更文件 — 97.9%
+按时间范围+定向状态导出变更文件 — 2.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="16" customHeight="1">
       <c r="A357" s="41" t="n"/>
       <c r="B357" s="23" t="inlineStr">
         <is>
@@ -18396,8 +18529,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="358">
+      <c r="F357" s="44" t="inlineStr">
+        <is>
+          <t>按BatchId查询批量操作明细日志 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="16" customHeight="1">
       <c r="A358" s="41" t="n"/>
       <c r="B358" s="27" t="inlineStr">
         <is>
@@ -18419,8 +18557,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="359">
+      <c r="F358" s="44" t="inlineStr">
+        <is>
+          <t>查询批量操作日志列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="16" customHeight="1">
       <c r="A359" s="41" t="n"/>
       <c r="B359" s="23" t="inlineStr">
         <is>
@@ -18442,8 +18585,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="360">
+      <c r="F359" s="44" t="inlineStr">
+        <is>
+          <t>按BatchId查询预算变更明细日志 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="16" customHeight="1">
       <c r="A360" s="41" t="n"/>
       <c r="B360" s="27" t="inlineStr">
         <is>
@@ -18465,13 +18613,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>查询批量操作日志列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
+      <c r="F360" s="44" t="inlineStr">
+        <is>
+          <t>获取Campaign改名类变更日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="16" customHeight="1">
       <c r="A361" s="41" t="n"/>
       <c r="B361" s="23" t="inlineStr">
         <is>
@@ -18493,8 +18641,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="362">
+      <c r="F361" s="44" t="inlineStr">
+        <is>
+          <t>按BatchId查询命名变更明细日志 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="16" customHeight="1">
       <c r="A362" s="41" t="n"/>
       <c r="B362" s="27" t="inlineStr">
         <is>
@@ -18516,8 +18669,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="363">
+      <c r="F362" s="44" t="inlineStr">
+        <is>
+          <t>查询命名变更日志列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="16" customHeight="1">
       <c r="A363" s="41" t="n"/>
       <c r="B363" s="23" t="inlineStr">
         <is>
@@ -18539,8 +18697,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="364">
+      <c r="F363" s="44" t="inlineStr">
+        <is>
+          <t>预览广告组改名文件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="16" customHeight="1">
       <c r="A364" s="41" t="n"/>
       <c r="B364" s="27" t="inlineStr">
         <is>
@@ -18562,8 +18725,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="365">
+      <c r="F364" s="44" t="inlineStr">
+        <is>
+          <t>预览预算变更文件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="16" customHeight="1">
       <c r="A365" s="41" t="n"/>
       <c r="B365" s="23" t="inlineStr">
         <is>
@@ -18585,8 +18753,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="366">
+      <c r="F365" s="44" t="inlineStr">
+        <is>
+          <t>预览Campaign改名文件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="16" customHeight="1">
       <c r="A366" s="41" t="n"/>
       <c r="B366" s="27" t="inlineStr">
         <is>
@@ -18608,8 +18781,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="367">
+      <c r="F366" s="44" t="inlineStr">
+        <is>
+          <t>预览状态变更文件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="32" customHeight="1">
       <c r="A367" s="41" t="n"/>
       <c r="B367" s="23" t="inlineStr">
         <is>
@@ -18631,8 +18809,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="368">
+      <c r="F367" s="44" t="inlineStr">
+        <is>
+          <t>预览定向出价变更文件 — 98%
+预览定向状态变更文件 — 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="32" customHeight="1">
       <c r="A368" s="41" t="n"/>
       <c r="B368" s="27" t="inlineStr">
         <is>
@@ -18652,6 +18836,12 @@
       <c r="E368" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F368" s="44" t="inlineStr">
+        <is>
+          <t>预览新建否定定向文件 — 65.4%
+预览新建正向定向文件 — 34.6%</t>
         </is>
       </c>
     </row>
@@ -18816,7 +19006,7 @@
         </is>
       </c>
     </row>
-    <row r="376">
+    <row r="376" ht="16" customHeight="1">
       <c r="A376" s="41" t="n"/>
       <c r="B376" s="27" t="inlineStr">
         <is>
@@ -18838,8 +19028,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="377">
+      <c r="F376" s="44" t="inlineStr">
+        <is>
+          <t>校验批量上传Excel文件类型 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="16" customHeight="1">
       <c r="A377" s="41" t="n"/>
       <c r="B377" s="23" t="inlineStr">
         <is>
@@ -18861,8 +19056,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="378">
+      <c r="F377" s="44" t="inlineStr">
+        <is>
+          <t>校验批量改预算文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="16" customHeight="1">
       <c r="A378" s="41" t="n"/>
       <c r="B378" s="27" t="inlineStr">
         <is>
@@ -18884,9 +19084,9 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>确认并执行广告组改名(含后置还原,可重复)</t>
+      <c r="F378" s="44" t="inlineStr">
+        <is>
+          <t>校验批量改名文件</t>
         </is>
       </c>
     </row>
@@ -27859,7 +28059,7 @@
         </is>
       </c>
     </row>
-    <row r="720">
+    <row r="720" ht="32" customHeight="1">
       <c r="A720" s="41" t="n"/>
       <c r="B720" s="26" t="inlineStr">
         <is>
@@ -27881,8 +28081,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="721">
+      <c r="F720" s="44" t="inlineStr">
+        <is>
+          <t>带过滤条件全选待打标Campaign — 60.6%
+不带过滤条件全选全部Campaign — 39.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="721" ht="16" customHeight="1">
       <c r="A721" s="41" t="n"/>
       <c r="B721" s="23" t="inlineStr">
         <is>
@@ -27904,8 +28110,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="722" ht="16" customHeight="1">
+      <c r="F721" s="44" t="inlineStr">
+        <is>
+          <t>按campaignTag查询自动打标规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="722" ht="32" customHeight="1">
       <c r="A722" s="41" t="n"/>
       <c r="B722" s="27" t="inlineStr">
         <is>
@@ -27929,11 +28140,12 @@
       </c>
       <c r="F722" s="44" t="inlineStr">
         <is>
-          <t>Campaign子标签报表数据 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="723" ht="16" customHeight="1">
+          <t>按SubTagId过滤查看子标签数据 — 55.9%
+旧版结构按CampaignTagId过滤汇总(不含SubTag) — 44.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="723" ht="48" customHeight="1">
       <c r="A723" s="41" t="n"/>
       <c r="B723" s="23" t="inlineStr">
         <is>
@@ -27957,11 +28169,13 @@
       </c>
       <c r="F723" s="44" t="inlineStr">
         <is>
-          <t>Campaign子标签分组聚合数据 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="724" ht="16" customHeight="1">
+          <t>按date维度分组查询子标签数据 — 71.4%
+按week维度分组查询子标签数据 — 19%
+按month维度分组查询子标签数据 — 9.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="724" ht="32" customHeight="1">
       <c r="A724" s="41" t="n"/>
       <c r="B724" s="27" t="inlineStr">
         <is>
@@ -27985,11 +28199,12 @@
       </c>
       <c r="F724" s="44" t="inlineStr">
         <is>
-          <t>按Campaign查其所属标签 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="725" ht="16" customHeight="1">
+          <t>查询单个Campaign的标签 — 48%
+批量查询多个Campaign的标签 — 5.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="725" ht="32" customHeight="1">
       <c r="A725" s="41" t="n"/>
       <c r="B725" s="23" t="inlineStr">
         <is>
@@ -28013,11 +28228,12 @@
       </c>
       <c r="F725" s="44" t="inlineStr">
         <is>
-          <t>Campaign标签报表列表页 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="726" ht="16" customHeight="1">
+          <t>按CampaignTagId过滤查看标签列表页 — 21.6%
+不筛选标签查看全部标签列表页 — 78.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="726" ht="32" customHeight="1">
       <c r="A726" s="41" t="n"/>
       <c r="B726" s="27" t="inlineStr">
         <is>
@@ -28041,7 +28257,8 @@
       </c>
       <c r="F726" s="44" t="inlineStr">
         <is>
-          <t>Campaign标签报表汇总行 — 100%</t>
+          <t>按CampaignTagId过滤查看标签汇总 — 22.5%
+不筛选标签查看全部标签汇总 — 77.5%</t>
         </is>
       </c>
     </row>
@@ -28069,11 +28286,11 @@
       </c>
       <c r="F727" s="44" t="inlineStr">
         <is>
-          <t>获取Campaign标签用户列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="728" ht="16" customHeight="1">
+          <t>查询CampaignTag相关用户列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="728" ht="32" customHeight="1">
       <c r="A728" s="41" t="n"/>
       <c r="B728" s="27" t="inlineStr">
         <is>
@@ -28097,7 +28314,8 @@
       </c>
       <c r="F728" s="44" t="inlineStr">
         <is>
-          <t>Campaign标签趋势图 — 100%</t>
+          <t>按date维度查看标签趋势图 — 51%
+按ytd维度查看子标签趋势图 — 46%</t>
         </is>
       </c>
     </row>
@@ -28509,7 +28727,7 @@
         </is>
       </c>
     </row>
-    <row r="743">
+    <row r="743" ht="48" customHeight="1">
       <c r="A743" s="41" t="n"/>
       <c r="B743" s="24" t="inlineStr">
         <is>
@@ -28531,8 +28749,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="744">
+      <c r="F743" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单批次复制SB创意文案与素材到已有广告组 — 100%
+场景1: 不修改广告活动名称批量复制SB创意到已有广告组 — 50%
+场景2: 修改广告活动名称批量复制SB创意到已有广告组 — 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="744" ht="48" customHeight="1">
       <c r="A744" s="41" t="n"/>
       <c r="B744" s="27" t="inlineStr">
         <is>
@@ -28554,8 +28779,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="745">
+      <c r="F744" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单批次复制SD创意文案与素材到已有广告组 — 100%
+场景1: 不修改广告活动名称复制SD创意到已有广告组 — 33.3%
+场景2: 修改广告活动名称复制SD创意到已有广告组 — 66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="745" ht="32" customHeight="1">
       <c r="A745" s="41" t="n"/>
       <c r="B745" s="23" t="inlineStr">
         <is>
@@ -28577,8 +28809,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="746">
+      <c r="F745" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按ASSET TYPE+扩展名筛选素材库并按创建时间倒序分页 — 100%
+场景1: 按ASSET TYPE+扩展名+ASSET ID筛选素材库并按创建时间倒序分页 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" ht="32" customHeight="1">
       <c r="A746" s="41" t="n"/>
       <c r="B746" s="27" t="inlineStr">
         <is>
@@ -28600,9 +28838,10 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F746" t="inlineStr">
-        <is>
-          <t>场景1: 单批次复制SB创意文案与素材到已有广告组</t>
+      <c r="F746" s="44" t="inlineStr">
+        <is>
+          <t>场景1: Copy后重命名广告活动 — 100%
+场景1: Copy后重命名广告活动 — 100%</t>
         </is>
       </c>
     </row>
@@ -29126,7 +29365,7 @@
         </is>
       </c>
     </row>
-    <row r="765">
+    <row r="765" ht="160" customHeight="1">
       <c r="A765" s="41" t="n"/>
       <c r="B765" s="24" t="inlineStr">
         <is>
@@ -29148,1479 +29387,7 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="766">
-      <c r="A766" s="41" t="n"/>
-      <c r="B766" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C766" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D766" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/DownloadHourlyPlacementTrend</t>
-        </is>
-      </c>
-      <c r="E766" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" s="41" t="n"/>
-      <c r="B767" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C767" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D767" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/DownloadHourlyPlacementWeekTrend</t>
-        </is>
-      </c>
-      <c r="E767" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" s="41" t="n"/>
-      <c r="B768" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C768" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D768" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/DownloadHourlyWeekTrend</t>
-        </is>
-      </c>
-      <c r="E768" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" s="41" t="n"/>
-      <c r="B769" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C769" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D769" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetAMCAudienceReportCampaignData</t>
-        </is>
-      </c>
-      <c r="E769" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" s="41" t="n"/>
-      <c r="B770" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C770" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D770" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetAMCAudienceReportCampaignTotal</t>
-        </is>
-      </c>
-      <c r="E770" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" s="41" t="n"/>
-      <c r="B771" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C771" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D771" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetAMCAudienceReportChart</t>
-        </is>
-      </c>
-      <c r="E771" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" s="41" t="n"/>
-      <c r="B772" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C772" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D772" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetAMCAudienceReportDetails</t>
-        </is>
-      </c>
-      <c r="E772" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" s="41" t="n"/>
-      <c r="B773" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C773" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D773" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetAMCAudienceReportList</t>
-        </is>
-      </c>
-      <c r="E773" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" s="41" t="n"/>
-      <c r="B774" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C774" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D774" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetAMCAudienceReportTotal</t>
-        </is>
-      </c>
-      <c r="E774" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" s="41" t="n"/>
-      <c r="B775" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C775" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D775" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetASINBrandHaloReport</t>
-        </is>
-      </c>
-      <c r="E775" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" s="41" t="n"/>
-      <c r="B776" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C776" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D776" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetAccountProfileSpendReport</t>
-        </is>
-      </c>
-      <c r="E776" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" s="41" t="n"/>
-      <c r="B777" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C777" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D777" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetBrandMetricsBrand</t>
-        </is>
-      </c>
-      <c r="E777" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" s="41" t="n"/>
-      <c r="B778" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C778" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D778" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetBrandMetricsBrandKeywrodsReport</t>
-        </is>
-      </c>
-      <c r="E778" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" s="41" t="n"/>
-      <c r="B779" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C779" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D779" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetBrandMetricsCategory</t>
-        </is>
-      </c>
-      <c r="E779" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" s="41" t="n"/>
-      <c r="B780" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C780" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D780" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetBrandMetricsCustomerReport</t>
-        </is>
-      </c>
-      <c r="E780" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" s="41" t="n"/>
-      <c r="B781" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C781" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D781" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetBrandMetricsNTBAnalysisReport</t>
-        </is>
-      </c>
-      <c r="E781" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" s="41" t="n"/>
-      <c r="B782" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C782" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D782" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetBrandMetricsReport</t>
-        </is>
-      </c>
-      <c r="E782" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" s="41" t="n"/>
-      <c r="B783" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C783" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D783" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignActive</t>
-        </is>
-      </c>
-      <c r="E783" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" s="41" t="n"/>
-      <c r="B784" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C784" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D784" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignDailyPerformanceTrend</t>
-        </is>
-      </c>
-      <c r="E784" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" s="41" t="n"/>
-      <c r="B785" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C785" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D785" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignDailyPerformanceTrendTotal</t>
-        </is>
-      </c>
-      <c r="E785" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" s="41" t="n"/>
-      <c r="B786" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C786" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D786" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignOutofBudget</t>
-        </is>
-      </c>
-      <c r="E786" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" s="41" t="n"/>
-      <c r="B787" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C787" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D787" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignPerformance</t>
-        </is>
-      </c>
-      <c r="E787" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" s="41" t="n"/>
-      <c r="B788" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C788" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D788" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignPerformanceByCampaignType</t>
-        </is>
-      </c>
-      <c r="E788" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" s="41" t="n"/>
-      <c r="B789" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C789" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D789" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignPerformanceByTargetingType</t>
-        </is>
-      </c>
-      <c r="E789" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" s="41" t="n"/>
-      <c r="B790" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C790" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D790" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignPlacement</t>
-        </is>
-      </c>
-      <c r="E790" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" s="41" t="n"/>
-      <c r="B791" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C791" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D791" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignPlacementAnalysis</t>
-        </is>
-      </c>
-      <c r="E791" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" s="41" t="n"/>
-      <c r="B792" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C792" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D792" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTagALLSubTag</t>
-        </is>
-      </c>
-      <c r="E792" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" s="41" t="n"/>
-      <c r="B793" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C793" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D793" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTagActive</t>
-        </is>
-      </c>
-      <c r="E793" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" s="41" t="n"/>
-      <c r="B794" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C794" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D794" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTagPerformance</t>
-        </is>
-      </c>
-      <c r="E794" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" s="41" t="n"/>
-      <c r="B795" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C795" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D795" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTagSubTag</t>
-        </is>
-      </c>
-      <c r="E795" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" s="41" t="n"/>
-      <c r="B796" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C796" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D796" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTagTimeTypePerformance</t>
-        </is>
-      </c>
-      <c r="E796" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" s="41" t="n"/>
-      <c r="B797" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C797" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D797" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTop10ASIN</t>
-        </is>
-      </c>
-      <c r="E797" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" s="41" t="n"/>
-      <c r="B798" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C798" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D798" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTop10Campaign</t>
-        </is>
-      </c>
-      <c r="E798" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" s="41" t="n"/>
-      <c r="B799" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C799" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D799" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTop10Keyword</t>
-        </is>
-      </c>
-      <c r="E799" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" s="41" t="n"/>
-      <c r="B800" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C800" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D800" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTop10PAT</t>
-        </is>
-      </c>
-      <c r="E800" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" s="41" t="n"/>
-      <c r="B801" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C801" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D801" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTopMovers</t>
-        </is>
-      </c>
-      <c r="E801" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" s="41" t="n"/>
-      <c r="B802" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C802" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D802" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetCampaignTopPerformance</t>
-        </is>
-      </c>
-      <c r="E802" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" s="41" t="n"/>
-      <c r="B803" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C803" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D803" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetDailyPerformanceTrend</t>
-        </is>
-      </c>
-      <c r="E803" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" s="41" t="n"/>
-      <c r="B804" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C804" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D804" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetDailyPerformanceTrendTotal</t>
-        </is>
-      </c>
-      <c r="E804" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" s="41" t="n"/>
-      <c r="B805" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C805" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D805" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTotal</t>
-        </is>
-      </c>
-      <c r="E805" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" s="41" t="n"/>
-      <c r="B806" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C806" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D806" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTotalOlap</t>
-        </is>
-      </c>
-      <c r="E806" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" s="41" t="n"/>
-      <c r="B807" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C807" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D807" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTrand</t>
-        </is>
-      </c>
-      <c r="E807" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" s="41" t="n"/>
-      <c r="B808" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C808" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D808" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTrandOlap</t>
-        </is>
-      </c>
-      <c r="E808" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" s="41" t="n"/>
-      <c r="B809" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C809" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D809" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordByCampaignType</t>
-        </is>
-      </c>
-      <c r="E809" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" s="41" t="n"/>
-      <c r="B810" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C810" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D810" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordByMatchType</t>
-        </is>
-      </c>
-      <c r="E810" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" s="41" t="n"/>
-      <c r="B811" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C811" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D811" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordOfSearchterm</t>
-        </is>
-      </c>
-      <c r="E811" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" s="41" t="n"/>
-      <c r="B812" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C812" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D812" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordPerformance</t>
-        </is>
-      </c>
-      <c r="E812" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" s="41" t="n"/>
-      <c r="B813" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C813" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D813" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordTopMovers</t>
-        </is>
-      </c>
-      <c r="E813" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" s="41" t="n"/>
-      <c r="B814" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C814" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D814" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordTopMoversOfNewKeyword</t>
-        </is>
-      </c>
-      <c r="E814" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" s="41" t="n"/>
-      <c r="B815" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C815" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D815" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordTopPerformance</t>
-        </is>
-      </c>
-      <c r="E815" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" s="41" t="n"/>
-      <c r="B816" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C816" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D816" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetKeywordTopPerformanceForMatchtype</t>
-        </is>
-      </c>
-      <c r="E816" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" s="41" t="n"/>
-      <c r="B817" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C817" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D817" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetPerformance</t>
-        </is>
-      </c>
-      <c r="E817" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" s="41" t="n"/>
-      <c r="B818" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C818" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D818" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetPerformanceTotal</t>
-        </is>
-      </c>
-      <c r="E818" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="819">
-      <c r="A819" s="41" t="n"/>
-      <c r="B819" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C819" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D819" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductDailyPerformanceTrend</t>
-        </is>
-      </c>
-      <c r="E819" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" s="41" t="n"/>
-      <c r="B820" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C820" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D820" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductDailyPerformanceTrendTotal</t>
-        </is>
-      </c>
-      <c r="E820" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" s="41" t="n"/>
-      <c r="B821" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C821" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D821" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductEligibilityCheck</t>
-        </is>
-      </c>
-      <c r="E821" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" s="41" t="n"/>
-      <c r="B822" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C822" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D822" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductEligibilityReport</t>
-        </is>
-      </c>
-      <c r="E822" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" s="41" t="n"/>
-      <c r="B823" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C823" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D823" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductPerformance</t>
-        </is>
-      </c>
-      <c r="E823" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" s="41" t="n"/>
-      <c r="B824" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C824" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D824" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductPerformanceByCampaignType</t>
-        </is>
-      </c>
-      <c r="E824" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="825">
-      <c r="A825" s="41" t="n"/>
-      <c r="B825" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C825" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D825" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductTopMovers</t>
-        </is>
-      </c>
-      <c r="E825" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" s="41" t="n"/>
-      <c r="B826" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C826" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D826" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProductTopPerformance</t>
-        </is>
-      </c>
-      <c r="E826" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="827">
-      <c r="A827" s="41" t="n"/>
-      <c r="B827" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C827" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D827" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProfileByCampaignType</t>
-        </is>
-      </c>
-      <c r="E827" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" s="41" t="n"/>
-      <c r="B828" s="27" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C828" s="27" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D828" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetProfileTimeTypePerformance</t>
-        </is>
-      </c>
-      <c r="E828" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" s="41" t="n"/>
-      <c r="B829" s="23" t="inlineStr">
-        <is>
-          <t>DefaultReport</t>
-        </is>
-      </c>
-      <c r="C829" s="23" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D829" s="23" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/GetVersion05171040</t>
-        </is>
-      </c>
-      <c r="E829" s="8" t="inlineStr">
-        <is>
-          <t>limin</t>
-        </is>
-      </c>
-      <c r="F829" t="inlineStr">
+      <c r="F765" s="44" t="inlineStr">
         <is>
           <t>全部Profile+无过滤 — 36.2%
 单Profile+无过滤 — 22.6%
@@ -30635,29 +29402,1845 @@
         </is>
       </c>
     </row>
-    <row r="830">
-      <c r="A830" s="41" t="n"/>
-      <c r="B830" s="27" t="inlineStr">
+    <row r="766" ht="128" customHeight="1">
+      <c r="A766" s="41" t="n"/>
+      <c r="B766" s="27" t="inlineStr">
         <is>
           <t>DefaultReport</t>
         </is>
       </c>
-      <c r="C830" s="27" t="inlineStr">
+      <c r="C766" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D766" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/DownloadHourlyPlacementTrend</t>
+        </is>
+      </c>
+      <c r="E766" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F766" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含Placement维度(IsPlacement=1) — 37.1%
+单Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 22.9%
+单Profile+按CampaignTag过滤+含Placement维度(IsPlacement=1) — 11.4%
+单Profile+按CampaignIds过滤+含Placement维度(IsPlacement=2) — 11.4%
+全部Profile+无过滤+含Placement维度(IsPlacement=1) — 8.6%
+全部Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 2.9%
+多Profile+按CampaignTag过滤+含环比对比(CompareType=2)+含Placement维度(IsPlacement=1) — 2.9%
+多Profile+无过滤+含Placement维度(IsPlacement=1) — 2.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="767" ht="32" customHeight="1">
+      <c r="A767" s="41" t="n"/>
+      <c r="B767" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C767" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D767" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/DownloadHourlyPlacementWeekTrend</t>
+        </is>
+      </c>
+      <c r="E767" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F767" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含Placement维度(IsPlacement=2) — 50.0%
+单Profile+无过滤+含Placement维度(IsPlacement=1) — 50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="768" ht="16" customHeight="1">
+      <c r="A768" s="41" t="n"/>
+      <c r="B768" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C768" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D768" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/DownloadHourlyWeekTrend</t>
+        </is>
+      </c>
+      <c r="E768" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F768" s="44" t="inlineStr">
+        <is>
+          <t>全部Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="769" ht="48" customHeight="1">
+      <c r="A769" s="41" t="n"/>
+      <c r="B769" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C769" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D769" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetAMCAudienceReportCampaignData</t>
+        </is>
+      </c>
+      <c r="E769" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F769" s="44" t="inlineStr">
+        <is>
+          <t>dim=ytd+单Profile+AudienceName+CampaignType — 63.6%
+dim=ytd+多Profile+AudienceName+CampaignType — 25.2%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 10.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="770" ht="112" customHeight="1">
+      <c r="A770" s="41" t="n"/>
+      <c r="B770" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C770" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D770" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetAMCAudienceReportCampaignTotal</t>
+        </is>
+      </c>
+      <c r="E770" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F770" s="44" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 43.2%
+dim=ytd+单Profile+CampaignType — 33.0%
+dim=ytd+单Profile+AudienceName+CampaignType — 10.2%
+dim=ytd+多Profile+AudienceName+CampaignType — 5.0%
+dim=ytd+单Profile+CampaignType+CampaignTag — 4.8%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 1.4%
+dim=ytd+单Profile+AudienceName+CampaignType+Portfolio — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="771" ht="160" customHeight="1">
+      <c r="A771" s="41" t="n"/>
+      <c r="B771" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C771" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D771" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetAMCAudienceReportChart</t>
+        </is>
+      </c>
+      <c r="E771" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F771" s="44" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 30.0%
+dim=ytd+单Profile+CampaignType — 23.4%
+dim=month+单Profile+AudienceName — 10.8%
+dim=week+单Profile+AudienceName — 7.2%
+dim=date+单Profile+AudienceName — 6.6%
+dim=ytd+单Profile+AudienceName+CampaignType — 5.8%
+dim=month+单Profile+AudienceName — 5.0%
+dim=ytd+多Profile+AudienceName+CampaignType — 4.6%
+dim=ytd+单Profile+CampaignType+CampaignTag — 4.0%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="772" ht="96" customHeight="1">
+      <c r="A772" s="41" t="n"/>
+      <c r="B772" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C772" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D772" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetAMCAudienceReportDetails</t>
+        </is>
+      </c>
+      <c r="E772" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F772" s="44" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 44.6%
+dim=ytd+单Profile+CampaignType — 31.0%
+dim=ytd+单Profile+AudienceName+CampaignType — 10.0%
+dim=ytd+多Profile+AudienceName+CampaignType — 7.2%
+dim=ytd+单Profile+CampaignType+CampaignTag — 3.2%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 2.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="773" ht="128" customHeight="1">
+      <c r="A773" s="41" t="n"/>
+      <c r="B773" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C773" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D773" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetAMCAudienceReportList</t>
+        </is>
+      </c>
+      <c r="E773" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F773" s="44" t="inlineStr">
+        <is>
+          <t>dim=ytd+单Profile+AudienceName — 39.6%
+dim=ytd+多Profile+CampaignType — 19.8%
+dim=ytd+单Profile+CampaignType — 15.4%
+dim=ytd+多Profile+AudienceName — 9.2%
+dim=ytd+单Profile+AudienceName+CampaignType — 5.8%
+dim=ytd+单Profile+CampaignType+CampaignTag — 3.2%
+dim=ytd+多Profile+AudienceName+CampaignType — 2.2%
+dim=ytd+单Profile+AudienceName+CampaignTag — 2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="774" ht="96" customHeight="1">
+      <c r="A774" s="41" t="n"/>
+      <c r="B774" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C774" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D774" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetAMCAudienceReportTotal</t>
+        </is>
+      </c>
+      <c r="E774" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F774" s="44" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 42.2%
+dim=ytd+单Profile+CampaignType — 35.8%
+dim=ytd+单Profile+AudienceName+CampaignType — 9.6%
+dim=ytd+多Profile+AudienceName+CampaignType — 6.4%
+dim=ytd+单Profile+CampaignType+CampaignTag — 3.0%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="775" ht="48" customHeight="1">
+      <c r="A775" s="41" t="n"/>
+      <c r="B775" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C775" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D775" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetASINBrandHaloReport</t>
+        </is>
+      </c>
+      <c r="E775" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F775" s="44" t="inlineStr">
+        <is>
+          <t>CampaignType=sponsoredProducts+无过滤 — 77.3%
+CampaignType=sponsoredProducts+ASIN过滤 — 17.3%
+CampaignType=SponsoredDisplay+无过滤 — 3.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="776" ht="32" customHeight="1">
+      <c r="A776" s="41" t="n"/>
+      <c r="B776" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C776" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D776" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetAccountProfileSpendReport</t>
+        </is>
+      </c>
+      <c r="E776" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F776" s="44" t="inlineStr">
+        <is>
+          <t>有Profile过滤+有Advertiser过滤 — 92.6%
+无Profile过滤+有Advertiser过滤 — 7.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="777" ht="16" customHeight="1">
+      <c r="A777" s="41" t="n"/>
+      <c r="B777" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C777" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D777" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetBrandMetricsBrand</t>
+        </is>
+      </c>
+      <c r="E777" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F777" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 99.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="778" ht="80" customHeight="1">
+      <c r="A778" s="41" t="n"/>
+      <c r="B778" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C778" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D778" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetBrandMetricsBrandKeywrodsReport</t>
+        </is>
+      </c>
+      <c r="E778" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F778" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+Brand=All+含Category+TimeType=1 — 62.8%
+单Profile+指定Brand+含Category+TimeType=1 — 12.6%
+单Profile+指定Brand+无Category+TimeType=1 — 12.4%
+单Profile+Brand=All+含Category+TimeType=0 — 9.4%
+单Profile+指定Brand+含Category+TimeType=3 — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="779" ht="32" customHeight="1">
+      <c r="A779" s="41" t="n"/>
+      <c r="B779" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C779" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D779" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetBrandMetricsCategory</t>
+        </is>
+      </c>
+      <c r="E779" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F779" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 81.4%
+多Profile+无过滤 — 18.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="780" ht="16" customHeight="1">
+      <c r="A780" s="41" t="n"/>
+      <c r="B780" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C780" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D780" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetBrandMetricsCustomerReport</t>
+        </is>
+      </c>
+      <c r="E780" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F780" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="781" ht="16" customHeight="1">
+      <c r="A781" s="41" t="n"/>
+      <c r="B781" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C781" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D781" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetBrandMetricsNTBAnalysisReport</t>
+        </is>
+      </c>
+      <c r="E781" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F781" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="782" ht="16" customHeight="1">
+      <c r="A782" s="41" t="n"/>
+      <c r="B782" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C782" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D782" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetBrandMetricsReport</t>
+        </is>
+      </c>
+      <c r="E782" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F782" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="783" ht="128" customHeight="1">
+      <c r="A783" s="41" t="n"/>
+      <c r="B783" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C783" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D783" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignActive</t>
+        </is>
+      </c>
+      <c r="E783" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F783" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 31.2%
+单Profile+无过滤 — 30.6%
+单Profile+按CampaignTag过滤 — 21.0%
+单Profile+无过滤+含环比(CompareType=2) — 5.6%
+全部Profile+无过滤 — 3.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+多Profile+按CampaignTag过滤 — 2.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="784" ht="160" customHeight="1">
+      <c r="A784" s="41" t="n"/>
+      <c r="B784" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C784" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D784" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignDailyPerformanceTrend</t>
+        </is>
+      </c>
+      <c r="E784" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F784" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 35.0%
+单Profile+无过滤 — 20.6%
+多Profile+无过滤 — 16.8%
+多Profile+按CampaignTag过滤 — 12.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 5.2%
+单Profile+无过滤+含环比(CompareType=2) — 2.8%
+全部Profile+无过滤 — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.4%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="785" ht="128" customHeight="1">
+      <c r="A785" s="41" t="n"/>
+      <c r="B785" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C785" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D785" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignDailyPerformanceTrendTotal</t>
+        </is>
+      </c>
+      <c r="E785" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F785" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 33.8%
+多Profile+无过滤 — 20.8%
+单Profile+无过滤 — 19.2%
+多Profile+按CampaignTag过滤 — 11.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 7.2%
+单Profile+无过滤+含环比(CompareType=2) — 3.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%
+全部Profile+无过滤 — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="786" ht="128" customHeight="1">
+      <c r="A786" s="41" t="n"/>
+      <c r="B786" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C786" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D786" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignOutofBudget</t>
+        </is>
+      </c>
+      <c r="E786" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F786" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 34.0%
+单Profile+无过滤 — 28.6%
+单Profile+按CampaignTag过滤 — 20.4%
+单Profile+无过滤+含环比(CompareType=2) — 5.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+全部Profile+无过滤 — 2.8%
+多Profile+按CampaignTag过滤 — 1.8%
+单Profile+无过滤+含环比(CompareType=1) — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="787" ht="128" customHeight="1">
+      <c r="A787" s="41" t="n"/>
+      <c r="B787" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C787" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D787" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignPerformance</t>
+        </is>
+      </c>
+      <c r="E787" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F787" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 33.2%
+多Profile+无过滤 — 22.6%
+单Profile+无过滤 — 21.4%
+多Profile+按CampaignTag过滤 — 11.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.4%
+单Profile+无过滤+含环比(CompareType=2) — 3.0%
+全部Profile+无过滤 — 1.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="788" ht="128" customHeight="1">
+      <c r="A788" s="41" t="n"/>
+      <c r="B788" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C788" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D788" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignPerformanceByCampaignType</t>
+        </is>
+      </c>
+      <c r="E788" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F788" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 41.2%
+单Profile+无过滤 — 25.2%
+单Profile+按CampaignTag过滤 — 23.8%
+多Profile+按CampaignTag过滤 — 2.4%
+全部Profile+无过滤 — 2.4%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.0%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="789" ht="128" customHeight="1">
+      <c r="A789" s="41" t="n"/>
+      <c r="B789" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C789" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D789" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignPerformanceByTargetingType</t>
+        </is>
+      </c>
+      <c r="E789" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F789" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 30.8%
+多Profile+无过滤 — 30.8%
+单Profile+按CampaignTag过滤 — 21.6%
+单Profile+无过滤+含环比(CompareType=2) — 5.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+多Profile+按CampaignTag过滤 — 2.8%
+全部Profile+无过滤 — 2.0%
+单Profile+无过滤+含环比(CompareType=1) — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="790" ht="128" customHeight="1">
+      <c r="A790" s="41" t="n"/>
+      <c r="B790" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C790" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D790" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignPlacement</t>
+        </is>
+      </c>
+      <c r="E790" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F790" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 34.4%
+单Profile+无过滤 — 26.0%
+单Profile+按CampaignTag过滤 — 23.6%
+单Profile+无过滤+含环比(CompareType=2) — 4.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.2%
+全部Profile+无过滤 — 2.0%
+多Profile+按CampaignTag过滤 — 2.0%
+单Profile+无过滤+含环比(CompareType=1) — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="791" ht="128" customHeight="1">
+      <c r="A791" s="41" t="n"/>
+      <c r="B791" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C791" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D791" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignPlacementAnalysis</t>
+        </is>
+      </c>
+      <c r="E791" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F791" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 34.4%
+单Profile+无过滤 — 33.6%
+单Profile+按CampaignTag过滤 — 19.0%
+单Profile+无过滤+含环比(CompareType=2) — 3.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+多Profile+按CampaignTag过滤 — 2.0%
+全部Profile+无过滤 — 2.0%
+多Profile+无过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="792" ht="96" customHeight="1">
+      <c r="A792" s="41" t="n"/>
+      <c r="B792" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C792" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D792" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTagALLSubTag</t>
+        </is>
+      </c>
+      <c r="E792" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F792" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 59.8%
+多Profile+按CampaignTag过滤 — 29.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 6.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.4%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="793" ht="112" customHeight="1">
+      <c r="A793" s="41" t="n"/>
+      <c r="B793" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C793" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D793" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTagActive</t>
+        </is>
+      </c>
+      <c r="E793" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F793" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 55.6%
+多Profile+按CampaignTag过滤 — 28.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 6.4%
+单Profile+无过滤 — 3.8%
+多Profile+无过滤 — 2.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="794" ht="128" customHeight="1">
+      <c r="A794" s="41" t="n"/>
+      <c r="B794" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C794" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D794" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTagPerformance</t>
+        </is>
+      </c>
+      <c r="E794" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F794" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 56.0%
+多Profile+按CampaignTag过滤 — 26.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 7.2%
+单Profile+无过滤 — 2.8%
+多Profile+无过滤 — 2.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.2%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="795" ht="80" customHeight="1">
+      <c r="A795" s="41" t="n"/>
+      <c r="B795" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C795" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D795" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTagSubTag</t>
+        </is>
+      </c>
+      <c r="E795" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F795" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 61.0%
+多Profile+无过滤 — 27.6%
+单Profile+无过滤+含环比(CompareType=2) — 7.2%
+单Profile+无过滤+含环比(CompareType=1) — 2.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="796" ht="112" customHeight="1">
+      <c r="A796" s="41" t="n"/>
+      <c r="B796" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C796" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D796" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTagTimeTypePerformance</t>
+        </is>
+      </c>
+      <c r="E796" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F796" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 60.2%
+多Profile+按CampaignTag过滤 — 28.2%
+单Profile+无过滤 — 3.8%
+多Profile+无过滤 — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="797" ht="128" customHeight="1">
+      <c r="A797" s="41" t="n"/>
+      <c r="B797" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C797" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D797" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTop10ASIN</t>
+        </is>
+      </c>
+      <c r="E797" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F797" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 31.4%
+单Profile+无过滤 — 30.8%
+单Profile+按CampaignTag过滤 — 24.0%
+单Profile+无过滤+含环比(CompareType=2) — 4.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+多Profile+按CampaignTag过滤 — 2.6%
+全部Profile+无过滤 — 2.0%
+多Profile+无过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="798" ht="112" customHeight="1">
+      <c r="A798" s="41" t="n"/>
+      <c r="B798" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C798" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D798" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTop10Campaign</t>
+        </is>
+      </c>
+      <c r="E798" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F798" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 32.8%
+单Profile+无过滤 — 32.8%
+单Profile+按CampaignTag过滤 — 20.8%
+单Profile+无过滤+含环比(CompareType=2) — 4.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.8%
+多Profile+按CampaignTag过滤 — 2.2%
+全部Profile+无过滤 — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="799" ht="128" customHeight="1">
+      <c r="A799" s="41" t="n"/>
+      <c r="B799" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C799" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D799" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTop10Keyword</t>
+        </is>
+      </c>
+      <c r="E799" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F799" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 32.4%
+单Profile+无过滤 — 29.4%
+单Profile+按CampaignTag过滤 — 21.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.4%
+单Profile+无过滤+含环比(CompareType=2) — 4.2%
+全部Profile+无过滤 — 2.4%
+多Profile+按CampaignTag过滤 — 2.2%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="800" ht="144" customHeight="1">
+      <c r="A800" s="41" t="n"/>
+      <c r="B800" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C800" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D800" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTop10PAT</t>
+        </is>
+      </c>
+      <c r="E800" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F800" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 31.8%
+单Profile+无过滤 — 27.6%
+单Profile+按CampaignTag过滤 — 23.0%
+单Profile+无过滤+含环比(CompareType=2) — 5.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.4%
+多Profile+按CampaignTag过滤 — 2.6%
+全部Profile+无过滤 — 1.8%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="801" ht="128" customHeight="1">
+      <c r="A801" s="41" t="n"/>
+      <c r="B801" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C801" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D801" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTopMovers</t>
+        </is>
+      </c>
+      <c r="E801" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F801" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 33.8%
+单Profile+按CampaignTag过滤 — 22.4%
+单Profile+无过滤 — 13.6%
+多Profile+无过滤 — 12.6%
+多Profile+按CampaignTag过滤 — 9.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="802" ht="96" customHeight="1">
+      <c r="A802" s="41" t="n"/>
+      <c r="B802" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C802" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D802" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetCampaignTopPerformance</t>
+        </is>
+      </c>
+      <c r="E802" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F802" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 55.6%
+多Profile+按CampaignTag过滤 — 25.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 8.2%
+单Profile+无过滤 — 4.2%
+多Profile+无过滤 — 2.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="803" ht="64" customHeight="1">
+      <c r="A803" s="41" t="n"/>
+      <c r="B803" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C803" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D803" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetDailyPerformanceTrend</t>
+        </is>
+      </c>
+      <c r="E803" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F803" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 86.4%
+多Profile+无过滤 — 7.4%
+单Profile+无过滤+含环比(CompareType=1) — 3.0%
+单Profile+无过滤+含环比(CompareType=2) — 2.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="804" ht="16" customHeight="1">
+      <c r="A804" s="41" t="n"/>
+      <c r="B804" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C804" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D804" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetDailyPerformanceTrendTotal</t>
+        </is>
+      </c>
+      <c r="E804" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F804" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="805" ht="16" customHeight="1">
+      <c r="A805" s="41" t="n"/>
+      <c r="B805" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C805" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D805" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTotal</t>
+        </is>
+      </c>
+      <c r="E805" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F805" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含环比对比(CompareType=2) — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="806" ht="144" customHeight="1">
+      <c r="A806" s="41" t="n"/>
+      <c r="B806" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C806" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D806" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTotalOlap</t>
+        </is>
+      </c>
+      <c r="E806" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F806" s="44" t="inlineStr">
+        <is>
+          <t>全部Profile+无过滤 — 38.6%
+单Profile+无过滤 — 24.6%
+单Profile+按CampaignTag过滤 — 13.4%
+单Profile+按CampaignIds过滤 — 11.4%
+全部Profile+按CampaignTag过滤 — 4.2%
+全部Profile+按CampaignIds过滤 — 2.2%
+多Profile+按CampaignIds过滤 — 1.0%
+多Profile+无过滤 — 1.0%
+单Profile+无过滤+含环比对比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="807" ht="32" customHeight="1">
+      <c r="A807" s="41" t="n"/>
+      <c r="B807" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C807" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D807" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTrand</t>
+        </is>
+      </c>
+      <c r="E807" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F807" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含环比对比(CompareType=2) — 50.0%
+单Profile+无过滤+含环比对比(CompareType=2)+含Placement维度(IsPlacement=1) — 50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="808" ht="208" customHeight="1">
+      <c r="A808" s="41" t="n"/>
+      <c r="B808" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C808" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D808" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetDefaultHourlyPerformanceTrandOlap</t>
+        </is>
+      </c>
+      <c r="E808" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F808" s="44" t="inlineStr">
+        <is>
+          <t>全部Profile+无过滤 — 19.4%
+全部Profile+无过滤+含Placement维度(IsPlacement=1) — 18.6%
+单Profile+无过滤+含Placement维度(IsPlacement=1) — 12.6%
+单Profile+无过滤 — 11.4%
+单Profile+按CampaignTag过滤 — 7.4%
+单Profile+按CampaignIds过滤 — 6.4%
+单Profile+按CampaignTag过滤+含Placement维度(IsPlacement=1) — 4.8%
+单Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 4.0%
+全部Profile+按CampaignTag过滤 — 2.0%
+全部Profile+按CampaignTag过滤+含Placement维度(IsPlacement=1) — 1.6%
+全部Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 1.4%
+全部Profile+按CampaignIds过滤 — 1.4%
+单Profile+无过滤+含Placement维度(IsPlacement=2) — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="809" ht="16" customHeight="1">
+      <c r="A809" s="41" t="n"/>
+      <c r="B809" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C809" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D809" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordByCampaignType</t>
+        </is>
+      </c>
+      <c r="E809" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F809" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="810" ht="128" customHeight="1">
+      <c r="A810" s="41" t="n"/>
+      <c r="B810" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C810" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D810" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordByMatchType</t>
+        </is>
+      </c>
+      <c r="E810" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F810" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 29.6%
+单Profile+无过滤 — 26.0%
+单Profile+按CampaignTag过滤 — 19.8%
+多Profile+按CampaignTag过滤 — 15.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.8%
+多Profile+无过滤+含环比(CompareType=2) — 1.2%
+单Profile+无过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="811" ht="144" customHeight="1">
+      <c r="A811" s="41" t="n"/>
+      <c r="B811" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C811" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D811" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordOfSearchterm</t>
+        </is>
+      </c>
+      <c r="E811" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F811" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 30.8%
+多Profile+无过滤 — 27.4%
+单Profile+按CampaignTag过滤 — 16.8%
+多Profile+按CampaignTag过滤 — 14.4%
+单Profile+无过滤+含环比(CompareType=2) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.6%
+多Profile+无过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="812" ht="144" customHeight="1">
+      <c r="A812" s="41" t="n"/>
+      <c r="B812" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C812" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D812" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordPerformance</t>
+        </is>
+      </c>
+      <c r="E812" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F812" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 30.0%
+单Profile+无过滤 — 28.4%
+单Profile+按CampaignTag过滤 — 15.4%
+多Profile+按CampaignTag过滤 — 13.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.6%
+单Profile+无过滤+含环比(CompareType=2) — 1.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.6%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="813" ht="128" customHeight="1">
+      <c r="A813" s="41" t="n"/>
+      <c r="B813" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C813" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D813" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordTopMovers</t>
+        </is>
+      </c>
+      <c r="E813" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F813" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 28.8%
+单Profile+无过滤 — 26.4%
+单Profile+按CampaignTag过滤 — 19.2%
+多Profile+按CampaignTag过滤 — 13.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.6%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="814" ht="144" customHeight="1">
+      <c r="A814" s="41" t="n"/>
+      <c r="B814" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C814" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D814" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordTopMoversOfNewKeyword</t>
+        </is>
+      </c>
+      <c r="E814" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F814" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 29.6%
+单Profile+无过滤 — 26.4%
+单Profile+按CampaignTag过滤 — 19.4%
+多Profile+按CampaignTag过滤 — 14.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.2%
+单Profile+无过滤+含环比(CompareType=2) — 1.8%
+多Profile+无过滤+含环比(CompareType=2) — 1.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="815" ht="128" customHeight="1">
+      <c r="A815" s="41" t="n"/>
+      <c r="B815" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C815" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D815" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordTopPerformance</t>
+        </is>
+      </c>
+      <c r="E815" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F815" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 29.2%
+多Profile+无过滤 — 28.4%
+单Profile+按CampaignTag过滤 — 20.4%
+多Profile+按CampaignTag过滤 — 12.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.6%
+单Profile+无过滤+含环比(CompareType=2) — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="816" ht="80" customHeight="1">
+      <c r="A816" s="41" t="n"/>
+      <c r="B816" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C816" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D816" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetKeywordTopPerformanceForMatchtype</t>
+        </is>
+      </c>
+      <c r="E816" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F816" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 53.2%
+单Profile+按CampaignTag过滤 — 35.4%
+单Profile+无过滤+含环比(CompareType=1) — 5.1%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.8%
+单Profile+无过滤+含环比(CompareType=2) — 2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="817" ht="64" customHeight="1">
+      <c r="A817" s="41" t="n"/>
+      <c r="B817" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C817" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D817" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetPerformance</t>
+        </is>
+      </c>
+      <c r="E817" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F817" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 84.4%
+多Profile+无过滤 — 7.6%
+单Profile+无过滤+含环比(CompareType=2) — 4.2%
+单Profile+无过滤+含环比(CompareType=1) — 3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="818" ht="64" customHeight="1">
+      <c r="A818" s="41" t="n"/>
+      <c r="B818" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C818" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D818" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetPerformanceTotal</t>
+        </is>
+      </c>
+      <c r="E818" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F818" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 85.6%
+多Profile+无过滤 — 7.8%
+单Profile+无过滤+含环比(CompareType=2) — 2.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="819" ht="128" customHeight="1">
+      <c r="A819" s="41" t="n"/>
+      <c r="B819" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C819" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D819" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductDailyPerformanceTrend</t>
+        </is>
+      </c>
+      <c r="E819" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F819" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 46.0%
+单Profile+无过滤 — 34.0%
+单Profile+按CampaignTag过滤 — 9.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.2%
+多Profile+按CampaignTag过滤 — 2.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.4%
+全部Profile+无过滤 — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="820" ht="128" customHeight="1">
+      <c r="A820" s="41" t="n"/>
+      <c r="B820" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C820" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D820" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductDailyPerformanceTrendTotal</t>
+        </is>
+      </c>
+      <c r="E820" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F820" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 46.2%
+单Profile+无过滤 — 35.6%
+单Profile+按CampaignTag过滤 — 9.4%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.8%
+单Profile+无过滤+含环比(CompareType=1) — 1.4%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%
+多Profile+按CampaignTag过滤 — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="821" ht="48" customHeight="1">
+      <c r="A821" s="41" t="n"/>
+      <c r="B821" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C821" s="23" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D830" s="27" t="inlineStr">
-        <is>
-          <t>/api/DefaultReport/v3/TestLan</t>
-        </is>
-      </c>
-      <c r="E830" s="8" t="inlineStr">
+      <c r="D821" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductEligibilityCheck</t>
+        </is>
+      </c>
+      <c r="E821" s="8" t="inlineStr">
         <is>
           <t>limin</t>
         </is>
       </c>
-      <c r="F830" t="inlineStr">
+      <c r="F821" s="44" t="inlineStr">
         <is>
           <t>type=sp — 85.0%
 type=sb — 13.9%
@@ -30665,6 +31248,290 @@
         </is>
       </c>
     </row>
+    <row r="822" ht="96" customHeight="1">
+      <c r="A822" s="41" t="n"/>
+      <c r="B822" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C822" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D822" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductEligibilityReport</t>
+        </is>
+      </c>
+      <c r="E822" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F822" s="44" t="inlineStr">
+        <is>
+          <t>全部Profile+无状态过滤 — 48.8%
+单Profile+无状态过滤 — 33.6%
+多Profile+无状态过滤 — 10.6%
+单Profile+eligibilityStatus=ELIGIBLE WITH WARNING — 2.8%
+单Profile+eligibilityStatus=INELIGIBLE — 1.8%
+多Profile+eligibilityStatus=INELIGIBLE — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="823" ht="112" customHeight="1">
+      <c r="A823" s="41" t="n"/>
+      <c r="B823" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C823" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D823" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductPerformance</t>
+        </is>
+      </c>
+      <c r="E823" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F823" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 44.2%
+单Profile+无过滤 — 36.4%
+单Profile+按CampaignTag过滤 — 10.0%
+多Profile+按CampaignTag过滤 — 2.2%
+单Profile+无过滤+含环比(CompareType=1) — 1.8%
+多Profile+无过滤+含环比(CompareType=1) — 1.4%
+单Profile+无过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="824" ht="96" customHeight="1">
+      <c r="A824" s="41" t="n"/>
+      <c r="B824" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C824" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D824" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductPerformanceByCampaignType</t>
+        </is>
+      </c>
+      <c r="E824" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F824" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 53.8%
+单Profile+无过滤 — 30.4%
+单Profile+按CampaignTag过滤 — 7.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.4%
+单Profile+无过滤+含环比(CompareType=2) — 1.6%
+多Profile+按CampaignTag过滤 — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="825" ht="112" customHeight="1">
+      <c r="A825" s="41" t="n"/>
+      <c r="B825" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C825" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D825" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductTopMovers</t>
+        </is>
+      </c>
+      <c r="E825" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F825" s="44" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 43.8%
+单Profile+无过滤 — 36.8%
+单Profile+按CampaignTag过滤 — 10.2%
+单Profile+无过滤+含环比(CompareType=1) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.6%
+单Profile+无过滤+含环比(CompareType=2) — 1.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="826" ht="112" customHeight="1">
+      <c r="A826" s="41" t="n"/>
+      <c r="B826" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C826" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D826" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProductTopPerformance</t>
+        </is>
+      </c>
+      <c r="E826" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F826" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 43.6%
+多Profile+无过滤 — 37.8%
+单Profile+按CampaignTag过滤 — 8.6%
+单Profile+无过滤+含环比(CompareType=1) — 3.0%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+多Profile+按CampaignTag过滤 — 1.6%
+多Profile+无过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="827" ht="16" customHeight="1">
+      <c r="A827" s="41" t="n"/>
+      <c r="B827" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C827" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D827" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProfileByCampaignType</t>
+        </is>
+      </c>
+      <c r="E827" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F827" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="828" ht="80" customHeight="1">
+      <c r="A828" s="41" t="n"/>
+      <c r="B828" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C828" s="27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D828" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetProfileTimeTypePerformance</t>
+        </is>
+      </c>
+      <c r="E828" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F828" s="44" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 86.0%
+多Profile+无过滤 — 6.6%
+单Profile+无过滤+含环比(CompareType=2) — 2.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.6%
+多Profile+无过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="829" ht="16" customHeight="1">
+      <c r="A829" s="41" t="n"/>
+      <c r="B829" s="23" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C829" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D829" s="23" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/GetVersion05171040</t>
+        </is>
+      </c>
+      <c r="E829" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F829" s="44" t="inlineStr">
+        <is>
+          <t>版本号查询(无业务参数) — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="830" ht="16" customHeight="1">
+      <c r="A830" s="41" t="n"/>
+      <c r="B830" s="27" t="inlineStr">
+        <is>
+          <t>DefaultReport</t>
+        </is>
+      </c>
+      <c r="C830" s="27" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D830" s="27" t="inlineStr">
+        <is>
+          <t>/api/DefaultReport/v3/TestLan</t>
+        </is>
+      </c>
+      <c r="E830" s="8" t="inlineStr">
+        <is>
+          <t>limin</t>
+        </is>
+      </c>
+      <c r="F830" s="44" t="inlineStr">
+        <is>
+          <t>健康检查/语言测试(无业务参数) — 100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="831" ht="90" customHeight="1">
       <c r="A831" s="41" t="n"/>
       <c r="B831" s="24" t="inlineStr">
@@ -30889,7 +31756,7 @@
         </is>
       </c>
     </row>
-    <row r="839">
+    <row r="839" ht="16" customHeight="1">
       <c r="A839" s="41" t="n"/>
       <c r="B839" s="24" t="inlineStr">
         <is>
@@ -30911,8 +31778,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="840">
+      <c r="F839" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按Profile+Campaign+AdGroup查询广告组Explorer详情 — 99.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="840" ht="16" customHeight="1">
       <c r="A840" s="41" t="n"/>
       <c r="B840" s="27" t="inlineStr">
         <is>
@@ -30934,8 +31806,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="841">
+      <c r="F840" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按Profile+Campaign查询广告活动Explorer详情 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="841" ht="32" customHeight="1">
       <c r="A841" s="41" t="n"/>
       <c r="B841" s="23" t="inlineStr">
         <is>
@@ -30957,8 +31834,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="842">
+      <c r="F841" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 全量Portfolio交互数据按Spend排序 不过滤名称 — 77.9%
+场景2: 按dimName关键词过滤Portfolio交互数据 — 20.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="842" ht="16" customHeight="1">
       <c r="A842" s="41" t="n"/>
       <c r="B842" s="27" t="inlineStr">
         <is>
@@ -30980,8 +31863,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="843">
+      <c r="F842" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按Profile+Portfolio查询组合Explorer详情 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="843" ht="16" customHeight="1">
       <c r="A843" s="41" t="n"/>
       <c r="B843" s="23" t="inlineStr">
         <is>
@@ -31003,9 +31891,9 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F843" t="inlineStr">
-        <is>
-          <t>场景1: 按Profile+Campaign+AdGroup查询广告组Explorer详情 — 99.6%</t>
+      <c r="F843" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按ProfileId查询Profile级Explorer详情 — 99.6%</t>
         </is>
       </c>
     </row>

--- a/single-api/mainapi/swagger_modules.xlsx
+++ b/single-api/mainapi/swagger_modules.xlsx
@@ -5362,7 +5362,7 @@
       </c>
       <c r="F9" s="44" t="inlineStr">
         <is>
-          <t>暂停指定广告并还原(含后置清理,可重复)</t>
+          <t>暂停指定广告并还原(含后置清理,可重复) — 33.3%</t>
         </is>
       </c>
     </row>
@@ -5390,11 +5390,11 @@
       </c>
       <c r="F10" s="44" t="inlineStr">
         <is>
-          <t>US ytd 默认 AdState 趋势
-US ytd Campaign下钻趋势
-US ytd 广告组下钻趋势
-US ytd SP/SD 广告类型筛选趋势
-JP ytd 默认市场趋势</t>
+          <t>US ytd 默认 AdState 趋势 — 15.6%
+US ytd Campaign下钻趋势 — 21.4%
+US ytd 广告组下钻趋势 — 3.0%
+US ytd SP/SD 广告类型筛选趋势 — 4.0%
+JP ytd 默认市场趋势 — 1.8%</t>
         </is>
       </c>
     </row>
@@ -5422,11 +5422,11 @@
       </c>
       <c r="F11" s="44" t="inlineStr">
         <is>
-          <t>US ytd 默认列表 pageSize=25
-US ytd Campaign下钻 pageSize=100
-US ytd 广告名称搜索
-US ytd 广告组下钻列表
-JP ytd 默认列表</t>
+          <t>US ytd 默认列表 pageSize=25 — 19.0%
+US ytd Campaign下钻 pageSize=100 — 17.2%
+US ytd 广告名称搜索 — 10.4%
+US ytd 广告组下钻列表 — 3.0%
+JP ytd 默认列表 — 3.0%</t>
         </is>
       </c>
     </row>
@@ -5454,9 +5454,9 @@
       </c>
       <c r="F12" s="44" t="inlineStr">
         <is>
-          <t>Campaign+AdGroup 拉取广告
-仅 AdGroup 拉取广告
-Campaign+AdGroup 按 ASIN 名称搜索</t>
+          <t>Campaign+AdGroup 拉取广告 — 80.8%
+仅 AdGroup 拉取广告 — 18.8%
+Campaign+AdGroup 按 ASIN 名称搜索 — 0.3%</t>
         </is>
       </c>
     </row>
@@ -5484,14 +5484,14 @@
       </c>
       <c r="F13" s="44" t="inlineStr">
         <is>
-          <t>US ytd 默认合计 pageSize=25
-US ytd Campaign下钻合计 pageSize=100
-US ytd 广告名称搜索合计
-JP ytd 默认市场合计</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>US ytd 默认合计 pageSize=25 — 15.8%
+US ytd Campaign下钻合计 pageSize=100 — 20.6%
+US ytd 广告名称搜索合计 — 5.6%
+JP ytd 默认市场合计 — 3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="41" t="n"/>
       <c r="B14" s="22" t="inlineStr">
         <is>
@@ -5511,6 +5511,11 @@
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t>按Profile+日期查询Portfolio广告主体明细（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -5907,10 +5912,10 @@
       </c>
       <c r="F27" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign下钻
-US ytd 默认浏览
-US ytd Campaign+CostType
-US ytd SegmentName搜索</t>
+          <t>US ytd Campaign下钻 — 53.6%
+US ytd 默认浏览 — 10.4%
+US ytd Campaign+CostType — 8.8%
+US ytd SegmentName搜索 — 3.2%</t>
         </is>
       </c>
     </row>
@@ -5938,10 +5943,10 @@
       </c>
       <c r="F28" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign下钻 pageSize=100
-US ytd Campaign+CostType pageSize=100
-US ytd 默认浏览 pageSize=100
-US ytd 默认浏览 pageSize=25</t>
+          <t>US ytd Campaign下钻 pageSize=100 — 50.8%
+US ytd Campaign+CostType pageSize=100 — 9.0%
+US ytd 默认浏览 pageSize=100 — 6.2%
+US ytd 默认浏览 pageSize=25 — 2.8%</t>
         </is>
       </c>
     </row>
@@ -5969,10 +5974,10 @@
       </c>
       <c r="F29" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign下钻 pageSize=100
-US ytd 默认浏览 pageSize=100
-US ytd Campaign+CostType pageSize=100
-US ytd 默认浏览 pageSize=25</t>
+          <t>US ytd Campaign下钻 pageSize=100 — 46.0%
+US ytd 默认浏览 pageSize=100 — 7.4%
+US ytd Campaign+CostType pageSize=100 — 7.2%
+US ytd 默认浏览 pageSize=25 — 3.8%</t>
         </is>
       </c>
     </row>
@@ -6000,11 +6005,11 @@
       </c>
       <c r="F30" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign下钻
-US ytd 默认浏览
-UK ytd 默认浏览
-CA ytd Campaign下钻
-US ytd CampaignName搜索</t>
+          <t>US ytd Campaign下钻 — 42.6%
+US ytd 默认浏览 — 35.2%
+UK ytd 默认浏览 — 5.2%
+CA ytd Campaign下钻 — 2.2%
+US ytd CampaignName搜索 — 2.0%</t>
         </is>
       </c>
     </row>
@@ -6032,11 +6037,11 @@
       </c>
       <c r="F31" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign下钻 pageSize=100
-US ytd 默认浏览 pageSize=100
-US ytd 默认浏览 pageSize=25
-US ytd Campaign下钻 pageSize=25
-UK ytd 默认浏览 pageSize=100</t>
+          <t>US ytd Campaign下钻 pageSize=100 — 34.0%
+US ytd 默认浏览 pageSize=100 — 21.2%
+US ytd 默认浏览 pageSize=25 — 13.0%
+US ytd Campaign下钻 pageSize=25 — 6.8%
+UK ytd 默认浏览 pageSize=100 — 5.6%</t>
         </is>
       </c>
     </row>
@@ -6064,11 +6069,11 @@
       </c>
       <c r="F32" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign下钻 pageSize=100
-US ytd 默认浏览 pageSize=100
-US ytd 默认浏览 pageSize=25
-US ytd Campaign下钻 pageSize=25
-UK ytd 默认浏览 pageSize=100</t>
+          <t>US ytd Campaign下钻 pageSize=100 — 30.4%
+US ytd 默认浏览 pageSize=100 — 23.4%
+US ytd 默认浏览 pageSize=25 — 12.2%
+US ytd Campaign下钻 pageSize=25 — 7.4%
+UK ytd 默认浏览 pageSize=100 — 5.6%</t>
         </is>
       </c>
     </row>
@@ -6096,9 +6101,9 @@
       </c>
       <c r="F33" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign+PlacementTypes
-US ytd Campaign+CostType+PlacementTypes
-US ytd Feed模式 Campaign+PlacementTypes</t>
+          <t>US ytd Campaign+PlacementTypes — 76.2%
+US ytd Campaign+CostType+PlacementTypes — 11.4%
+US ytd Feed模式 Campaign+PlacementTypes — 3.0%</t>
         </is>
       </c>
     </row>
@@ -6126,11 +6131,11 @@
       </c>
       <c r="F34" s="44" t="inlineStr">
         <is>
-          <t>US ytd CampaignName+State pageSize=10000
-US ytd CampaignType+Name+State pageSize=10000
-US ytd Campaign+State pageSize=10000
-US ytd Name+State+ServingStatus pageSize=10000
-US ytd Campaign下钻 pageSize=10000</t>
+          <t>US ytd CampaignName+State pageSize=10000 — 33.6%
+US ytd CampaignType+Name+State pageSize=10000 — 28.9%
+US ytd Campaign+State pageSize=10000 — 8.0%
+US ytd Name+State+ServingStatus pageSize=10000 — 7.7%
+US ytd Campaign下钻 pageSize=10000 — 3.8%</t>
         </is>
       </c>
     </row>
@@ -6158,10 +6163,10 @@
       </c>
       <c r="F35" s="44" t="inlineStr">
         <is>
-          <t>US ytd CampaignState默认 pageSize=25
-US ytd CampaignState默认 pageSize=500
-US ytd 默认浏览 pageSize=100
-US ytd CampaignType筛选 pageSize=100</t>
+          <t>US ytd CampaignState默认 pageSize=25 — 12.0%
+US ytd CampaignState默认 pageSize=500 — 10.6%
+US ytd 默认浏览 pageSize=100 — 7.0%
+US ytd CampaignType筛选 pageSize=100 — 6.2%</t>
         </is>
       </c>
     </row>
@@ -6189,11 +6194,11 @@
       </c>
       <c r="F36" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign+PlacementTypes pageSize=100
-US ytd Campaign+PlacementTypes pageSize=25
-US ytd Campaign+CostType+PlacementTypes pageSize=100
-US ytd Feed模式 Campaign+PlacementTypes pageSize=100
-US ytd Campaign+PlacementTypes pageSize=50</t>
+          <t>US ytd Campaign+PlacementTypes pageSize=100 — 63.8%
+US ytd Campaign+PlacementTypes pageSize=25 — 10.4%
+US ytd Campaign+CostType+PlacementTypes pageSize=100 — 7.2%
+US ytd Feed模式 Campaign+PlacementTypes pageSize=100 — 4.0%
+US ytd Campaign+PlacementTypes pageSize=50 — 3.0%</t>
         </is>
       </c>
     </row>
@@ -6221,10 +6226,10 @@
       </c>
       <c r="F37" s="44" t="inlineStr">
         <is>
-          <t>US ytd PlacementTypes默认
-US ytd Campaign+PlacementTypes
-US ytd CampaignName+PlacementTypes
-US ytd GroupBy=Placement</t>
+          <t>US ytd PlacementTypes默认 — 20.6%
+US ytd Campaign+PlacementTypes — 11.6%
+US ytd CampaignName+PlacementTypes — 4.6%
+US ytd GroupBy=Placement — 9.0%</t>
         </is>
       </c>
     </row>
@@ -6252,12 +6257,12 @@
       </c>
       <c r="F38" s="44" t="inlineStr">
         <is>
-          <t>US ytd Campaign+PlacementTypes pageSize=100
-US ytd Campaign+PlacementTypes pageSize=25
-US ytd Campaign+CostType+PlacementTypes pageSize=100
-US ytd PlacementTypes默认 pageSize=100
-US ytd PlacementTypes默认 pageSize=25
-US ytd GroupBy=Placement GroupByPlacement pageSize=100</t>
+          <t>US ytd Campaign+PlacementTypes pageSize=100 — 48.8%
+US ytd Campaign+PlacementTypes pageSize=25 — 8.6%
+US ytd Campaign+CostType+PlacementTypes pageSize=100 — 5.8%
+US ytd PlacementTypes默认 pageSize=100 — 3.6%
+US ytd PlacementTypes默认 pageSize=25 — 2.4%
+US ytd GroupBy=Placement GroupByPlacement pageSize=100 — 3.4%</t>
         </is>
       </c>
     </row>
@@ -6285,11 +6290,11 @@
       </c>
       <c r="F39" s="44" t="inlineStr">
         <is>
-          <t>US ytd PlacementTypes默认 pageSize=100
-US ytd PlacementTypes默认 pageSize=25
-US ytd Campaign+PlacementTypes pageSize=100
-US ytd CampaignName+PlacementTypes pageSize=100
-US ytd GroupBy=Placement GroupByPlacement pageSize=100</t>
+          <t>US ytd PlacementTypes默认 pageSize=100 — 13.4%
+US ytd PlacementTypes默认 pageSize=25 — 8.2%
+US ytd Campaign+PlacementTypes pageSize=100 — 7.6%
+US ytd CampaignName+PlacementTypes pageSize=100 — 5.0%
+US ytd GroupBy=Placement GroupByPlacement pageSize=100 — 10.8%</t>
         </is>
       </c>
     </row>
@@ -7208,12 +7213,12 @@
       </c>
       <c r="F69" s="44" t="inlineStr">
         <is>
-          <t>US 默认启用/暂停状态 100条分页
-US 按日维度广告活动下钻
-US 仅日期过滤无状态条件
-US 广告活动名称搜索
-US 25条分页默认状态
-US Feed模式列表</t>
+          <t>US 默认启用/暂停状态 100条分页 — 17.6%
+US 按日维度广告活动下钻 — 10.6%
+US 仅日期过滤无状态条件 — 10.0%
+US 广告活动名称搜索 — 8.2%
+US 25条分页默认状态 — 8.0%
+US Feed模式列表 — 3.2%</t>
         </is>
       </c>
     </row>
@@ -7241,11 +7246,11 @@
       </c>
       <c r="F70" s="44" t="inlineStr">
         <is>
-          <t>US 按日广告活动下钻图表
-US ytd 启用/暂停状态图表
-US 仅日期过滤图表
-US 广告活动名称搜索图表
-US Feed模式图表</t>
+          <t>US 按日广告活动下钻图表 — 31.0%
+US ytd 启用/暂停状态图表 — 20.8%
+US 仅日期过滤图表 — 10.2%
+US 广告活动名称搜索图表 — 7.2%
+US Feed模式图表 — 2.6%</t>
         </is>
       </c>
     </row>
@@ -7273,11 +7278,11 @@
       </c>
       <c r="F71" s="44" t="inlineStr">
         <is>
-          <t>US 默认启用/暂停状态汇总
-US 按日广告活动下钻汇总
-US 25条分页状态汇总
-US 仅日期过滤汇总
-US 广告活动名称搜索汇总</t>
+          <t>US 默认启用/暂停状态汇总 — 15.0%
+US 按日广告活动下钻汇总 — 13.4%
+US 25条分页状态汇总 — 7.8%
+US 仅日期过滤汇总 — 7.4%
+US 广告活动名称搜索汇总 — 6.4%</t>
         </is>
       </c>
     </row>
@@ -7446,9 +7451,9 @@
       </c>
       <c r="F77" s="44" t="inlineStr">
         <is>
-          <t>US 子标签绩效列表
-US Feed账号子标签列表
-US 精简字段子标签查询</t>
+          <t>US 子标签绩效列表 — 73.0%
+US Feed账号子标签列表 — 16.6%
+US 精简字段子标签查询 — 8.6%</t>
         </is>
       </c>
     </row>
@@ -7476,10 +7481,10 @@
       </c>
       <c r="F78" s="44" t="inlineStr">
         <is>
-          <t>US 默认汇总趋势
-US 指定关键词标签汇总
-JP 市场汇总趋势
-US 月度趋势</t>
+          <t>US 默认汇总趋势 — 49.0%
+US 指定关键词标签汇总 — 23.8%
+JP 市场汇总趋势 — 5.4%
+US 月度趋势 — 0.8%</t>
         </is>
       </c>
     </row>
@@ -7507,9 +7512,9 @@
       </c>
       <c r="F79" s="44" t="inlineStr">
         <is>
-          <t>US 默认标签列表
-JP 标签列表
-未指定市场标签列表
+          <t>US 默认标签列表 — 63.2%
+JP 标签列表 — 5.4%
+未指定市场标签列表 — 3.2%
 指定关键词标签筛选</t>
         </is>
       </c>
@@ -7538,10 +7543,10 @@
       </c>
       <c r="F80" s="44" t="inlineStr">
         <is>
-          <t>US 默认25条分页
-US 100条大页浏览
-US 指定标签100条分页
-US Feed账号100条分页</t>
+          <t>US 默认25条分页 — 30.0%
+US 100条大页浏览 — 17.2%
+US 指定标签100条分页 — 13.0%
+US Feed账号100条分页 — 2.0%</t>
         </is>
       </c>
     </row>
@@ -7569,10 +7574,10 @@
       </c>
       <c r="F81" s="44" t="inlineStr">
         <is>
-          <t>US 默认25条汇总
-US 100条汇总
-US 指定标签100条汇总
-US Feed账号100条汇总</t>
+          <t>US 默认25条汇总 — 27.6%
+US 100条汇总 — 17.8%
+US 指定标签100条汇总 — 12.4%
+US Feed账号100条汇总 — 2.2%</t>
         </is>
       </c>
     </row>
@@ -7824,12 +7829,12 @@
       </c>
       <c r="F90" s="44" t="inlineStr">
         <is>
-          <t>US Campaign 100条分页
-US Profile 100条分页
-US Campaign 25条分页
-CA Profile 100条分页
-US 名称关键词搜索
-US Enabled状态筛选
+          <t>US Campaign 100条分页 — 28.8%
+US Profile 100条分页 — 7.6%
+US Campaign 25条分页 — 6.0%
+CA Profile 100条分页 — 4.8%
+US 名称关键词搜索 — 2.4%
+US Enabled状态筛选 — 2.4%
 US Campaign与AdGroup钻取</t>
         </is>
       </c>
@@ -8461,7 +8466,7 @@
       </c>
       <c r="F111" s="44" t="inlineStr">
         <is>
-          <t>按搜索词添加标签并清理</t>
+          <t>按搜索词添加标签并清理 — 100%</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8494,7 @@
       </c>
       <c r="F112" s="44" t="inlineStr">
         <is>
-          <t>精确目标调价并还原</t>
+          <t>精确目标调价并还原 — 100%</t>
         </is>
       </c>
     </row>
@@ -8545,9 +8550,9 @@
       </c>
       <c r="F114" s="44" t="inlineStr">
         <is>
-          <t>US默认汇总趋势
-US活动钻取趋势
-US逐日趋势</t>
+          <t>US默认汇总趋势 — 13.8%
+US活动钻取趋势 — 29.2%
+US逐日趋势 — 8.6%</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8580,7 @@
       </c>
       <c r="F115" s="44" t="inlineStr">
         <is>
-          <t>查询搜索词否定状态</t>
+          <t>查询搜索词否定状态 — 100%</t>
         </is>
       </c>
     </row>
@@ -8603,8 +8608,8 @@
       </c>
       <c r="F116" s="44" t="inlineStr">
         <is>
-          <t>Click与ROAS筛选后全选
-零转化高点击筛选后全选</t>
+          <t>Click与ROAS筛选后全选 — 46.3%
+零转化高点击筛选后全选 — 4.9%</t>
         </is>
       </c>
     </row>
@@ -8632,10 +8637,10 @@
       </c>
       <c r="F117" s="44" t="inlineStr">
         <is>
-          <t>US活动钻取分页报表
-US默认分页报表
-大页导出浏览
-US逐日报表</t>
+          <t>US活动钻取分页报表 — 40.2%
+US默认分页报表 — 6.4%
+大页导出浏览 — 6.6%
+US逐日报表 — 4.4%</t>
         </is>
       </c>
     </row>
@@ -8663,9 +8668,9 @@
       </c>
       <c r="F118" s="44" t="inlineStr">
         <is>
-          <t>US默认汇总
-US活动钻取汇总
-US逐日口径汇总</t>
+          <t>US默认汇总 — 9.0%
+US活动钻取汇总 — 13.4%
+US逐日口径汇总 — 6.8%</t>
         </is>
       </c>
     </row>
@@ -8993,7 +8998,7 @@
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="16" customHeight="1">
       <c r="A131" s="41" t="n"/>
       <c r="B131" s="24" t="inlineStr">
         <is>
@@ -9015,8 +9020,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="132">
+      <c r="F131" s="39" t="inlineStr">
+        <is>
+          <t>无参获取天气预报列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" s="41" t="n"/>
       <c r="B132" s="22" t="inlineStr">
         <is>
@@ -9038,8 +9048,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="133">
+      <c r="F132" s="39" t="inlineStr">
+        <is>
+          <t>无参拉取活动与广告组合名称 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
       <c r="A133" s="41" t="n"/>
       <c r="B133" s="23" t="inlineStr">
         <is>
@@ -9061,8 +9076,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="134">
+      <c r="F133" s="39" t="inlineStr">
+        <is>
+          <t>无参拉取活动列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="16" customHeight="1">
       <c r="A134" s="41" t="n"/>
       <c r="B134" s="22" t="inlineStr">
         <is>
@@ -9084,8 +9104,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="135">
+      <c r="F134" s="39" t="inlineStr">
+        <is>
+          <t>无参诊断 Doris 字符集 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="16" customHeight="1">
       <c r="A135" s="41" t="n"/>
       <c r="B135" s="23" t="inlineStr">
         <is>
@@ -9107,8 +9132,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="136">
+      <c r="F135" s="39" t="inlineStr">
+        <is>
+          <t>无参拉取 Portfolio — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
       <c r="A136" s="42" t="n"/>
       <c r="B136" s="22" t="inlineStr">
         <is>
@@ -9128,6 +9158,11 @@
       <c r="E136" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F136" s="39" t="inlineStr">
+        <is>
+          <t>无参拉取小时报测试数据 — 100%</t>
         </is>
       </c>
     </row>
@@ -10029,6 +10064,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F36" s="39" t="inlineStr">
+        <is>
+          <t>⚠️ ES近90天/365天窗口内零真实调用样本，且Swagger未定义任何入参说明(无query/body字段)，无法确定真实调用结构，暂无法生成case，待人工提供接口文档或前端调用示例。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="41" t="n"/>
@@ -10052,6 +10092,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F37" s="39" t="inlineStr">
+        <is>
+          <t>⚠️ ES近90天/365天窗口内零真实调用样本，且Swagger未定义任何入参说明(无query/body字段)，无法确定真实调用结构，暂无法生成case，待人工提供接口文档或前端调用示例。</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="41" t="n"/>
@@ -10077,7 +10122,7 @@
       </c>
       <c r="F38" s="44" t="inlineStr">
         <is>
-          <t>校验用户名是否可用</t>
+          <t>校验用户名是否可用（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -10103,6 +10148,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F39" s="39" t="inlineStr">
+        <is>
+          <t>删除用户账号（ES无真实调用记录）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="41" t="n"/>
@@ -10126,6 +10176,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F40" s="39" t="inlineStr">
+        <is>
+          <t>解绑测试Amazon广告账号</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="41" t="n"/>
@@ -10176,6 +10231,11 @@
       <c r="E42" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F42" s="39" t="inlineStr">
+        <is>
+          <t>测试执行接口，无body定义</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10351,7 @@
       </c>
       <c r="F46" s="44" t="inlineStr">
         <is>
-          <t>按 DSP profileId 查托管广告主</t>
+          <t>按 DSP profileId 查托管广告主 — 100%</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10379,7 @@
       </c>
       <c r="F47" s="44" t="inlineStr">
         <is>
-          <t>按 advertiserId 查托管日志</t>
+          <t>按 advertiserId 查托管日志 — 100%</t>
         </is>
       </c>
     </row>
@@ -10343,6 +10403,11 @@
       <c r="E48" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F48" s="39" t="inlineStr">
+        <is>
+          <t>⚠️ ES近90天/365天窗口内零真实调用样本，且Swagger未定义任何入参说明(无query/body字段)，无法确定真实调用结构，暂无法生成case，待人工提供接口文档或前端调用示例。</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10495,7 @@
       </c>
       <c r="F51" s="44" t="inlineStr">
         <is>
-          <t>获取当前登录用户角色标志</t>
+          <t>获取当前登录用户角色标志 — 100%</t>
         </is>
       </c>
     </row>
@@ -10487,7 +10552,7 @@
       </c>
       <c r="F53" s="44" t="inlineStr">
         <is>
-          <t>无参拉取 Vendor 账号组</t>
+          <t>无参拉取 Vendor 账号组 — 100%</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10580,7 @@
       </c>
       <c r="F54" s="44" t="inlineStr">
         <is>
-          <t>无参查询当前用户标签权限开关</t>
+          <t>无参查询当前用户标签权限开关 — 100%</t>
         </is>
       </c>
     </row>
@@ -10541,6 +10606,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F55" s="39" t="inlineStr">
+        <is>
+          <t>用lmtesting111测试账号修改密码（ES无真实调用记录）</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="41" t="n"/>
@@ -10594,7 +10664,7 @@
       </c>
       <c r="F57" s="44" t="inlineStr">
         <is>
-          <t>修改 Profile 昵称后还原</t>
+          <t>修改 Profile 昵称后还原 — 100%</t>
         </is>
       </c>
     </row>
@@ -10648,6 +10718,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F59" s="39" t="inlineStr">
+        <is>
+          <t>设置用户角色/权限表单（ES无真实调用记录）</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="41" t="n"/>
@@ -10671,6 +10746,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F60" s="39" t="inlineStr">
+        <is>
+          <t>批量设置用户多Profile权限（ES无真实调用记录）</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="41" t="n"/>
@@ -10694,6 +10774,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F61" s="39" t="inlineStr">
+        <is>
+          <t>给lmtesting111分配现有测试Profile权限（ES无真实调用记录）</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="41" t="n"/>
@@ -10719,7 +10804,7 @@
       </c>
       <c r="F62" s="44" t="inlineStr">
         <is>
-          <t>修改 Vendor 账号名后还原</t>
+          <t>修改 Vendor 账号名后还原 — 100%</t>
         </is>
       </c>
     </row>
@@ -11299,10 +11384,10 @@
       </c>
       <c r="F85" s="44" t="inlineStr">
         <is>
-          <t>US ytd 子标签 pageSize=10000
-US ytd 子标签 pageSize=300
-DE ytd 子标签 pageSize=300
-CA ytd 子标签 pageSize=300</t>
+          <t>US ytd 子标签 pageSize=10000 — 33.9%
+US ytd 子标签 pageSize=300 — 32.1%
+DE ytd 子标签 pageSize=300 — 17.9%
+CA ytd 子标签 pageSize=300 — 7.1%</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11415,7 @@
       </c>
       <c r="F86" s="44" t="inlineStr">
         <is>
-          <t>默认拉取广告组标签树</t>
+          <t>默认拉取广告组标签树 — 100%</t>
         </is>
       </c>
     </row>
@@ -11358,11 +11443,11 @@
       </c>
       <c r="F87" s="44" t="inlineStr">
         <is>
-          <t>US ytd 默认汇总趋势
-US ytd UserId筛选趋势
-US ytd TagId筛选趋势
-DE date TagId日粒度趋势
-US date TagId日粒度趋势</t>
+          <t>US ytd 默认汇总趋势 — 50.7%
+US ytd UserId筛选趋势 — 9.2%
+US ytd TagId筛选趋势 — 9.2%
+DE date TagId日粒度趋势 — 7.4%
+US date TagId日粒度趋势 — 5.2%</t>
         </is>
       </c>
     </row>
@@ -11390,12 +11475,12 @@
       </c>
       <c r="F88" s="44" t="inlineStr">
         <is>
-          <t>US ytd 默认列表 pageSize=25
-US ytd UserId筛选 pageSize=25
-DE ytd TagId筛选 pageSize=300
-US ytd 列表 pageSize=100
-CA ytd TagId筛选 pageSize=300
-US ytd TagId筛选 pageSize=25</t>
+          <t>US ytd 默认列表 pageSize=25 — 42.9%
+US ytd UserId筛选 pageSize=25 — 9.8%
+DE ytd TagId筛选 pageSize=300 — 8.5%
+US ytd 列表 pageSize=100 — 8.5%
+CA ytd TagId筛选 pageSize=300 — 7.1%
+US ytd TagId筛选 pageSize=25 — 4.9%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11508,12 @@
       </c>
       <c r="F89" s="44" t="inlineStr">
         <is>
-          <t>US ytd 默认合计
-DE ytd TagId合计
-US ytd TagId合计
-CA ytd TagId合计
-US ytd UserId合计
-US ytd 合计 pageSize=100</t>
+          <t>US ytd 默认合计 — 33.1%
+DE ytd TagId合计 — 20.0%
+US ytd TagId合计 — 9.7%
+CA ytd TagId合计 — 9.0%
+US ytd UserId合计 — 7.6%
+US ytd 合计 pageSize=100 — 6.6%</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12595,7 @@
       </c>
       <c r="F127" s="44" t="inlineStr">
         <is>
-          <t>批量删除广告交易</t>
+          <t>批量删除广告交易（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -12538,7 +12623,7 @@
       </c>
       <c r="F128" s="44" t="inlineStr">
         <is>
-          <t>创建广告交易(Deal)</t>
+          <t>创建广告交易(Deal)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12679,7 @@
       </c>
       <c r="F130" s="44" t="inlineStr">
         <is>
-          <t>单条创建广告交易目标(含后置清理,可重复)</t>
+          <t>单条创建广告交易目标(含后置清理,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12707,7 @@
       </c>
       <c r="F131" s="44" t="inlineStr">
         <is>
-          <t>删除广告交易</t>
+          <t>删除广告交易（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12735,7 @@
       </c>
       <c r="F132" s="44" t="inlineStr">
         <is>
-          <t>删除广告交易目标</t>
+          <t>删除广告交易目标（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12850,7 @@
       </c>
       <c r="F136" s="44" t="inlineStr">
         <is>
-          <t>按单个dealId查询广告交易</t>
+          <t>按单个dealId查询广告交易 — 100%</t>
         </is>
       </c>
     </row>
@@ -12793,7 +12878,7 @@
       </c>
       <c r="F137" s="44" t="inlineStr">
         <is>
-          <t>按单个dealId查询交易目标</t>
+          <t>按单个dealId查询交易目标 — 100%</t>
         </is>
       </c>
     </row>
@@ -12821,7 +12906,7 @@
       </c>
       <c r="F138" s="44" t="inlineStr">
         <is>
-          <t>更新广告交易</t>
+          <t>更新广告交易（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -13276,12 +13361,12 @@
       </c>
       <c r="F154" s="44" t="inlineStr">
         <is>
-          <t>单ASIN+MANUAL默认排序推荐关键词
-Campaign+AdGroup去重推荐关键词
-2-5个ASIN批量MANUAL推荐
-单ASIN+AUTO FOR SALES推荐
-单ASIN+LEGACY FOR SALES推荐
-仅AdGroup(空campaignIds)推荐</t>
+          <t>单ASIN+MANUAL默认排序推荐关键词 — 35.2%
+Campaign+AdGroup去重推荐关键词 — 19.6%
+2-5个ASIN批量MANUAL推荐 — 11.2%
+单ASIN+AUTO FOR SALES推荐 — 5.0%
+单ASIN+LEGACY FOR SALES推荐 — 3.6%
+仅AdGroup(空campaignIds)推荐 — 3.0%</t>
         </is>
       </c>
     </row>
@@ -13309,9 +13394,9 @@
       </c>
       <c r="F155" s="44" t="inlineStr">
         <is>
-          <t>单ASIN默认count=50推荐商品
-单ASIN大页count=1000推荐商品
-多ASIN count=50推荐商品</t>
+          <t>单ASIN默认count=50推荐商品 — 97.4%
+单ASIN大页count=1000推荐商品 — 1.4%
+多ASIN count=50推荐商品 — 1.2%</t>
         </is>
       </c>
     </row>
@@ -13339,9 +13424,9 @@
       </c>
       <c r="F156" s="44" t="inlineStr">
         <is>
-          <t>单ASIN建议类目
-两个ASIN建议类目
-3-5个ASIN批量建议类目</t>
+          <t>单ASIN建议类目 — 52.4%
+两个ASIN建议类目 — 14.6%
+3-5个ASIN批量建议类目 — 15.0%</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13737,7 @@
       </c>
       <c r="F167" s="44" t="inlineStr">
         <is>
-          <t>按profile+campaign查活动表现(样本不足)</t>
+          <t>按profile+campaign查活动表现(样本不足)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -13680,8 +13765,8 @@
       </c>
       <c r="F168" s="44" t="inlineStr">
         <is>
-          <t>ytd否定词审计(广告活动层级level=1)
-ytd否定词审计(不限层级level=null)</t>
+          <t>ytd否定词审计(广告活动层级level=1) — 67.0%
+ytd否定词审计(不限层级level=null) — 33.0%</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14578,7 @@
       </c>
       <c r="F196" s="44" t="inlineStr">
         <is>
-          <t>批量添加ASIN为商品广告到指定Campaign/AdGroup[高风险-建议人工验证]</t>
+          <t>批量添加ASIN为商品广告到指定Campaign/AdGroup[高风险-建议人工验证]（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -14521,7 +14606,7 @@
       </c>
       <c r="F197" s="44" t="inlineStr">
         <is>
-          <t>按profile+campaign+adgroup批量查ASIN</t>
+          <t>按profile+campaign+adgroup批量查ASIN — 100%</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14690,7 @@
       </c>
       <c r="F200" s="44" t="inlineStr">
         <is>
-          <t>查ASIN主图URL</t>
+          <t>查ASIN主图URL — 100%</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14774,7 @@
       </c>
       <c r="F203" s="44" t="inlineStr">
         <is>
-          <t>按ASIN/SKU+profile搜索广告商品</t>
+          <t>按ASIN/SKU+profile搜索广告商品 — 100%</t>
         </is>
       </c>
     </row>
@@ -14717,7 +14802,7 @@
       </c>
       <c r="F204" s="44" t="inlineStr">
         <is>
-          <t>按SKU+profile搜索广告商品</t>
+          <t>按SKU+profile搜索广告商品 — 100%</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14830,7 @@
       </c>
       <c r="F205" s="44" t="inlineStr">
         <is>
-          <t>查用户ASIN追踪配额</t>
+          <t>查用户ASIN追踪配额 — 100%</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18363,7 @@
       </c>
       <c r="F348" s="44" t="inlineStr">
         <is>
-          <t>导出批量改名失败日志</t>
+          <t>导出批量改名失败日志（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18700,7 @@
       </c>
       <c r="F360" s="44" t="inlineStr">
         <is>
-          <t>获取Campaign改名类变更日志</t>
+          <t>获取Campaign改名类变更日志（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -18671,7 +18756,7 @@
       </c>
       <c r="F362" s="44" t="inlineStr">
         <is>
-          <t>查询命名变更日志列表</t>
+          <t>查询命名变更日志列表（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -18867,6 +18952,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F369" s="39" t="inlineStr">
+        <is>
+          <t>测试接口</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="41" t="n"/>
@@ -18890,6 +18980,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F370" s="39" t="inlineStr">
+        <is>
+          <t>测试接口</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="41" t="n"/>
@@ -18913,6 +19008,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F371" s="39" t="inlineStr">
+        <is>
+          <t>测试接口</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="41" t="n"/>
@@ -18936,6 +19036,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F372" s="39" t="inlineStr">
+        <is>
+          <t>测试接口</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="41" t="n"/>
@@ -18959,6 +19064,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F373" s="39" t="inlineStr">
+        <is>
+          <t>测试接口</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="41" t="n"/>
@@ -18982,6 +19092,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F374" s="39" t="inlineStr">
+        <is>
+          <t>测试接口</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="41" t="n"/>
@@ -19005,6 +19120,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F375" s="39" t="inlineStr">
+        <is>
+          <t>测试接口</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="16" customHeight="1">
       <c r="A376" s="41" t="n"/>
@@ -19058,7 +19178,7 @@
       </c>
       <c r="F377" s="44" t="inlineStr">
         <is>
-          <t>校验批量改预算文件</t>
+          <t>校验批量改预算文件（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -19086,7 +19206,7 @@
       </c>
       <c r="F378" s="44" t="inlineStr">
         <is>
-          <t>校验批量改名文件</t>
+          <t>校验批量改名文件（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24146,7 +24266,7 @@
       </c>
       <c r="F576" s="44" t="inlineStr">
         <is>
-          <t>在已有Campaign下新建广告组(含后置归档,可重复)</t>
+          <t>在已有Campaign下新建广告组(含后置归档,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24324,7 @@
       </c>
       <c r="F578" s="44" t="inlineStr">
         <is>
-          <t>跨广告组批量创建关键词(含后置归档,可重复)</t>
+          <t>跨广告组批量创建关键词(含后置归档,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24352,7 @@
       </c>
       <c r="F579" s="44" t="inlineStr">
         <is>
-          <t>跨Profile批量创建ASIN定向(含后置归档,可重复)</t>
+          <t>跨Profile批量创建ASIN定向(含后置归档,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24290,7 +24410,7 @@
       </c>
       <c r="F581" s="44" t="inlineStr">
         <is>
-          <t>创建SD广告系列(含后置归档,可重复)</t>
+          <t>创建SD广告系列(含后置归档,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24438,7 @@
       </c>
       <c r="F582" s="44" t="inlineStr">
         <is>
-          <t>在已有SD Campaign下创建广告组(含后置归档,可重复)</t>
+          <t>在已有SD Campaign下创建广告组(含后置归档,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24374,7 +24494,7 @@
       </c>
       <c r="F584" s="44" t="inlineStr">
         <is>
-          <t>查询ASIN广告资质状态</t>
+          <t>查询ASIN广告资质状态（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24522,7 @@
       </c>
       <c r="F585" s="44" t="inlineStr">
         <is>
-          <t>ASIN标签维度效果数据分页查询</t>
+          <t>ASIN标签维度效果数据分页查询（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24458,7 +24578,7 @@
       </c>
       <c r="F587" s="44" t="inlineStr">
         <is>
-          <t>按ASIN查询广告下商品广告</t>
+          <t>按ASIN查询广告下商品广告（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24542,7 +24662,7 @@
       </c>
       <c r="F590" s="44" t="inlineStr">
         <is>
-          <t>查询SD创意审核状态</t>
+          <t>查询SD创意审核状态（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24599,7 +24719,7 @@
       </c>
       <c r="F592" s="44" t="inlineStr">
         <is>
-          <t>按ASIN获取SD创意标题推荐</t>
+          <t>按ASIN获取SD创意标题推荐（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24772,7 +24892,7 @@
       </c>
       <c r="F598" s="44" t="inlineStr">
         <is>
-          <t>关键词/PAT批量建议出价(V4)</t>
+          <t>关键词/PAT批量建议出价(V4)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24800,7 +24920,7 @@
       </c>
       <c r="F599" s="44" t="inlineStr">
         <is>
-          <t>通过URL上传AI生成素材</t>
+          <t>通过URL上传AI生成素材（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -24884,7 +25004,7 @@
       </c>
       <c r="F602" s="44" t="inlineStr">
         <is>
-          <t>上传SD创意图片(multipart)</t>
+          <t>上传SD创意图片(multipart)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -28112,7 +28232,7 @@
       </c>
       <c r="F721" s="44" t="inlineStr">
         <is>
-          <t>按campaignTag查询自动打标规则</t>
+          <t>按campaignTag查询自动打标规则 — 100%</t>
         </is>
       </c>
     </row>
@@ -29490,7 +29610,7 @@
       </c>
       <c r="F768" s="44" t="inlineStr">
         <is>
-          <t>全部Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+          <t>全部Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -30676,7 +30796,7 @@
       </c>
       <c r="F804" s="44" t="inlineStr">
         <is>
-          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -30837,7 +30957,7 @@
       </c>
       <c r="F809" s="44" t="inlineStr">
         <is>
-          <t>多Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+          <t>多Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31560,7 @@
       </c>
       <c r="F827" s="44" t="inlineStr">
         <is>
-          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32969,7 @@
       </c>
       <c r="F876" s="44" t="inlineStr">
         <is>
-          <t>按国家查询亚马逊类目树</t>
+          <t>按国家查询亚马逊类目树（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -32933,7 +33053,7 @@
       </c>
       <c r="F879" s="44" t="inlineStr">
         <is>
-          <t>按搜索词+起始日期查询上周ASIN</t>
+          <t>按搜索词+起始日期查询上周ASIN（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -32961,7 +33081,7 @@
       </c>
       <c r="F880" s="44" t="inlineStr">
         <is>
-          <t>按搜索词查询最新ASIN</t>
+          <t>按搜索词查询最新ASIN（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -32989,7 +33109,7 @@
       </c>
       <c r="F881" s="44" t="inlineStr">
         <is>
-          <t>按搜索词批量查询最新搜索排名</t>
+          <t>按搜索词批量查询最新搜索排名（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33656,7 +33776,7 @@
       </c>
       <c r="F904" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33804,7 @@
       </c>
       <c r="F905" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33712,7 +33832,7 @@
       </c>
       <c r="F906" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33740,7 +33860,7 @@
       </c>
       <c r="F907" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33768,7 +33888,7 @@
       </c>
       <c r="F908" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33796,7 +33916,7 @@
       </c>
       <c r="F909" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33824,7 +33944,7 @@
       </c>
       <c r="F910" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33852,7 +33972,7 @@
       </c>
       <c r="F911" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33880,7 +34000,7 @@
       </c>
       <c r="F912" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33908,7 +34028,7 @@
       </c>
       <c r="F913" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33936,7 +34056,7 @@
       </c>
       <c r="F914" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33964,7 +34084,7 @@
       </c>
       <c r="F915" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -33992,7 +34112,7 @@
       </c>
       <c r="F916" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34140,7 @@
       </c>
       <c r="F917" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34168,7 @@
       </c>
       <c r="F918" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -34076,7 +34196,7 @@
       </c>
       <c r="F919" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -34104,7 +34224,7 @@
       </c>
       <c r="F920" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -34132,7 +34252,7 @@
       </c>
       <c r="F921" s="44" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Happy Path（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -36010,7 +36130,7 @@
         </is>
       </c>
     </row>
-    <row r="989" ht="16" customHeight="1">
+    <row r="989" ht="32" customHeight="1">
       <c r="A989" s="41" t="n"/>
       <c r="B989" s="24" t="inlineStr">
         <is>
@@ -36034,11 +36154,12 @@
       </c>
       <c r="F989" s="44" t="inlineStr">
         <is>
-          <t>关键词标签趋势图</t>
-        </is>
-      </c>
-    </row>
-    <row r="990" ht="16" customHeight="1">
+          <t>JP市场关键词标签趋势图 — 40%
+US市场关键词标签趋势图 — 60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="990" ht="48" customHeight="1">
       <c r="A990" s="41" t="n"/>
       <c r="B990" s="27" t="inlineStr">
         <is>
@@ -36062,11 +36183,13 @@
       </c>
       <c r="F990" s="44" t="inlineStr">
         <is>
-          <t>关键词标签报表列表页</t>
-        </is>
-      </c>
-    </row>
-    <row r="991" ht="16" customHeight="1">
+          <t>JP市场关键词标签明细列表(ROAS列,100条/页) — 40%
+US市场关键词标签明细列表(ACOS列,25条/页) — 40%
+US市场关键词标签明细列表(ROAS列,25条/页,长跨度日期) — 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="991" ht="48" customHeight="1">
       <c r="A991" s="41" t="n"/>
       <c r="B991" s="23" t="inlineStr">
         <is>
@@ -36090,7 +36213,9 @@
       </c>
       <c r="F991" s="44" t="inlineStr">
         <is>
-          <t>关键词标签报表汇总行</t>
+          <t>JP市场关键词标签汇总(ROAS列,100条/页) — 40%
+US市场关键词标签汇总(ACOS列,25条/页) — 40%
+US市场关键词标签汇总(ROAS列,25条/页,长跨度日期) — 20%</t>
         </is>
       </c>
     </row>
@@ -39072,7 +39197,7 @@
       </c>
       <c r="F1099" s="44" t="inlineStr">
         <is>
-          <t>场景1:Google登录授权回调(无ES样本)</t>
+          <t>场景1:Google登录授权回调(无ES样本)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -39100,7 +39225,7 @@
       </c>
       <c r="F1100" s="44" t="inlineStr">
         <is>
-          <t>场景1:通用授权回调(无ES样本)</t>
+          <t>场景1:通用授权回调(无ES样本)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -39128,7 +39253,7 @@
       </c>
       <c r="F1101" s="44" t="inlineStr">
         <is>
-          <t>场景1:测试重定向(无ES样本)</t>
+          <t>场景1:测试重定向(无ES样本)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -39156,7 +39281,7 @@
       </c>
       <c r="F1102" s="44" t="inlineStr">
         <is>
-          <t>场景1:测试Profile重定向(无ES样本)</t>
+          <t>场景1:测试Profile重定向(无ES样本)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -39269,7 +39394,7 @@
       </c>
       <c r="F1106" s="44" t="inlineStr">
         <is>
-          <t>场景1:单个广告活动加入Portfolio</t>
+          <t>场景1:单个广告活动加入Portfolio（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -39619,7 +39744,7 @@
       </c>
       <c r="F1118" s="44" t="inlineStr">
         <is>
-          <t>当前周期vs对比周期曝光下降查询</t>
+          <t>当前周期vs对比周期曝光下降查询（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -40420,7 +40545,7 @@
       </c>
       <c r="F1146" s="44" t="inlineStr">
         <is>
-          <t>下载H10 PAT研究表格</t>
+          <t>下载H10 PAT研究表格（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -40649,7 +40774,7 @@
       </c>
       <c r="F1154" s="44" t="inlineStr">
         <is>
-          <t>获取禁用Asin列表</t>
+          <t>获取禁用Asin列表（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -40677,7 +40802,7 @@
       </c>
       <c r="F1155" s="44" t="inlineStr">
         <is>
-          <t>获取图表默认Asin参数</t>
+          <t>获取图表默认Asin参数（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40858,7 @@
       </c>
       <c r="F1157" s="44" t="inlineStr">
         <is>
-          <t>获取H10黑盒过滤关键词数据</t>
+          <t>获取H10黑盒过滤关键词数据（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -40848,7 +40973,7 @@
       </c>
       <c r="F1161" s="44" t="inlineStr">
         <is>
-          <t>获取搜索词趋势图表数据</t>
+          <t>获取搜索词趋势图表数据（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42019,7 +42144,7 @@
       </c>
       <c r="F1202" s="44" t="inlineStr">
         <is>
-          <t>查询用户已选widget列表</t>
+          <t>查询用户已选widget列表（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42047,7 +42172,7 @@
       </c>
       <c r="F1203" s="44" t="inlineStr">
         <is>
-          <t>查询用户偏好设置</t>
+          <t>查询用户偏好设置（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42132,7 +42257,7 @@
       </c>
       <c r="F1206" s="44" t="inlineStr">
         <is>
-          <t>保存用户widget偏好</t>
+          <t>保存用户widget偏好（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42189,7 +42314,7 @@
       </c>
       <c r="F1208" s="44" t="inlineStr">
         <is>
-          <t>更新用户偏好设置</t>
+          <t>更新用户偏好设置（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42710,7 +42835,7 @@
       </c>
       <c r="F1228" s="44" t="inlineStr">
         <is>
-          <t>查询SB商品定向类目树</t>
+          <t>查询SB商品定向类目树（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42738,7 +42863,7 @@
       </c>
       <c r="F1229" s="44" t="inlineStr">
         <is>
-          <t>查询指定类目的细化定向条件</t>
+          <t>查询指定类目的细化定向条件（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42766,7 +42891,7 @@
       </c>
       <c r="F1230" s="44" t="inlineStr">
         <is>
-          <t>按类目查询商品定向匹配数量</t>
+          <t>按类目查询商品定向匹配数量（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -42794,7 +42919,7 @@
       </c>
       <c r="F1231" s="44" t="inlineStr">
         <is>
-          <t>按落地页ASIN查询成本控制推荐值</t>
+          <t>按落地页ASIN查询成本控制推荐值（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -43445,7 +43570,7 @@
       </c>
       <c r="F1254" s="44" t="inlineStr">
         <is>
-          <t>单profile+日期范围查询推荐ASIN</t>
+          <t>单profile+日期范围查询推荐ASIN（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -43977,7 +44102,7 @@
       </c>
       <c r="F1273" s="44" t="inlineStr">
         <is>
-          <t>查询广告组创意审核违规</t>
+          <t>查询广告组创意审核违规（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -44036,7 +44161,7 @@
       </c>
       <c r="F1275" s="44" t="inlineStr">
         <is>
-          <t>查询创意审核政策违规</t>
+          <t>查询创意审核政策违规（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -46780,7 +46905,7 @@
       </c>
       <c r="F1376" s="44" t="inlineStr">
         <is>
-          <t>空body调用</t>
+          <t>空body调用（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -47370,7 +47495,7 @@
       </c>
       <c r="F1397" s="44" t="inlineStr">
         <is>
-          <t>创建用户组(含后置清理,可重复)</t>
+          <t>创建用户组(含后置清理,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -47398,7 +47523,7 @@
       </c>
       <c r="F1398" s="44" t="inlineStr">
         <is>
-          <t>删除用户组(含前置创建,可重复)</t>
+          <t>删除用户组(含前置创建,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -47426,7 +47551,7 @@
       </c>
       <c r="F1399" s="44" t="inlineStr">
         <is>
-          <t>重命名用户组(含前置创建+后置清理,可重复)</t>
+          <t>重命名用户组(含前置创建+后置清理,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -47454,7 +47579,7 @@
       </c>
       <c r="F1400" s="44" t="inlineStr">
         <is>
-          <t>为用户组分配成员(含前置创建+后置清理,可重复)</t>
+          <t>为用户组分配成员(含前置创建+后置清理,可重复)（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
@@ -47482,7 +47607,7 @@
       </c>
       <c r="F1401" s="44" t="inlineStr">
         <is>
-          <t>查询当前账号全部用户组</t>
+          <t>查询当前账号全部用户组（ES无真实调用记录）</t>
         </is>
       </c>
     </row>
